--- a/new original/_Lang_Chinese/Lang/CN/Dialog/dialog.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr autoCompressPictures="1"/>
   <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="4"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="679">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -315,6 +315,15 @@
   </si>
   <si>
     <t xml:space="preserve">tail3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tail4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どうした{のだ}、#pc？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why are you looking at me, #pc?</t>
   </si>
   <si>
     <t xml:space="preserve">lockpick_purse</t>
@@ -737,6 +746,51 @@
   </si>
   <si>
     <t xml:space="preserve">...Do you recall when I told you, 'Don't lose it'? Here’s another, so take care of it this time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">はい…喜んで。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes...with pleasure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_deed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嬉しい{よ}。でも、挙式許可証が必要な{のだ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That makes me happy. But we need a Wedding Permit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嬉しい{よ}。でも、拠点でゆっくり話そう{よ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That makes me happy. But let's take our time and talk at home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本当に？（現在のパーティーは解散され、#tgと二人きりのパーティーが編成される）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are you serious? (Your current party is disbanded, and a new party is formed with just you and #tg.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_accept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嬉しい{よ}、#pc！ 私はとても幸せ{だ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm so happy, #pc! I'm truly happy.</t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -1133,6 +1187,57 @@
 How may I serve you today?</t>
   </si>
   <si>
+    <t xml:space="preserve">bottle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">リュシア|帰らぬ船|この瓶が誰かの手に届くなら、私はもう海の底でしょう。けれど空はとても青かった。
+名もなき兵士|最後の手紙|剣より重いのは恐怖だった。それでも私は逃げなかったと、誰かに知ってほしい。
+エルネス|潮騒の祈り|神よ、波を鎮める力がないなら、せめて眠りをください。
+ミレイユ|約束の浜辺|先に着いたら火を焚いて待っているわ。迷わず来て。
+航海士ダロス|星の記録|星は今日も正しかった。間違えたのは私だ。
+セレナ|ささやかな告白|あなたの名前を声に出せなかった。それだけが心残りです。
+老人|若き日へ|海は奪うが、すべてを無駄にはしない。生き延びろ。
+双子の妹|半分の世界|兄さん、世界はまだ半分残っているよ。だから帰ってきて。
+船医レナート|診療記録|傷は治せなかったが、痛みは和らげられた。それで十分だ。
+イザベル|歌の続きを|私がいなくても、この歌を最後まで歌って。
+密輸人カイル|報酬の行方|金は北の入り江に沈めた。欲しければ潜れ。
+神官見習いロア|疑いの告白|祈りは届かなかった。それでも私は祈ることをやめない。
+漁師ハルド|最後の漁|今日の獲物はなかった。でも海と話はできた。
+旅人シアン|通過点|ここは終わりじゃない。ただの通過点だ。
+王国書記官|公式記録抄|本船は嵐により喪失。以上。
+母|子へ|寒くなったら外套を着なさい。約束よ。
+吟遊詩人フェイ|未完成の詩|韻が足りない。続きを考えてくれる人へ。
+傭兵団長ヴォルク|撤退命令|生きて帰れ。名誉は後で拾えばいい。
+少女|はじめての旅|少し怖い。でも楽しい。
+誰か|拾ったあなたへ|あなたがこれを読んでいるなら、世界はまだ続いている。
+不明|お…|おうち…かえう…！
+不明|もう…|もうだめぽ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucia|The Ship That Never Returned|If this bottle reaches someone,I will likely be beneath the sea by then.But the sky was very blue.
+An Unnamed Soldier|Final Letter|Fear weighed heavier than my sword.But I want someone to know I did not run.
+Ernes|Prayer of the Surf|God,if you cannot calm the waves,then at least grant me sleep.
+Mireille|The Promised Shore|If I arrive first,I will light a fire and wait.Come without losing your way.
+Navigator Daros|Record of the Stars|The stars were correct again today.The one who erred was me.
+Selena|A Small Confession|I could never speak your name aloud.That is my only regret.
+Old Man|To My Younger Days|The sea takes much,but nothing is entirely wasted.Survive.
+The Younger Twin|Half the World Left|Brother,half the world is still here.So please come back.
+Ship Doctor Renato|Medical Notes|I could not heal the wounds,but I eased the pain.That was enough.
+Isabelle|Finish the Song|Even if I am gone,please sing this song to the end.
+Smuggler Kyle|Where the Payment Lies|The gold is sunk in the northern cove.Dive if you want it.
+Acolyte Roa|Confession of Doubt|My prayers were unanswered.Still,I will not stop praying.
+Fisherman Hald|The Last Catch|There was no catch today.But I spoke with the sea.
+Traveler Cyan|A Passing Point|This is not the end.It is only a passing point.
+Royal Scribe|Excerpt from Official Records|The vessel was lost to the storm.End of report.
+Mother|To My Child|Put on your cloak when it gets cold.Promise me.
+Bard Fey|An Unfinished Poem|The rhyme is missing.To whoever finishes it.
+Mercenary Captain Volk|Order to Retreat|Come back alive.Honor can be picked up later.
+Little Girl|My First Journey|I'm a little scared.But it's fun.
+Someone|To Whoever Finds This|If you are reading this,the world is still going on.
+Unknown|I...|I'm...going...home...!
+Unknown|I'm...|Moudamepo</t>
+  </si>
+  <si>
     <t xml:space="preserve">mysilia</t>
   </si>
   <si>
@@ -1417,6 +1522,23 @@
 Our great father oversees our penance, and there is no escape from our fates.
 As time passes, we grow less concerned with our material conditions...
 Yes #race, you're standing in front of an exile who has lived more than 1000 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mimu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">……ぴ？
+…………ぴぴ
+ピ………
+…ピぽ………
+……ぴ……エラー……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…Pi?
+……Pipi
+Pi………
+…Pipo………
+……Pi……Error……</t>
   </si>
   <si>
     <t xml:space="preserve">namamani</t>
@@ -2857,6 +2979,9 @@
     <t xml:space="preserve">好啊，先给{我}#1奥伦吧。</t>
   </si>
   <si>
+    <t xml:space="preserve">怎么了{。}，#pc？</t>
+  </si>
+  <si>
     <t xml:space="preserve">这好像是别人的遗失物{。}…算了，无所谓了{。}。</t>
   </si>
   <si>
@@ -2997,6 +3122,21 @@
   </si>
   <si>
     <t xml:space="preserve">…我不是告诉过你了吗？因为是重要的东西所以别弄丢了。 我再给你一张，这次要小心点啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的…我愿意。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好开心{。}。但必须要有婚礼许可证{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好开心{。}。但还是回到据点再慢慢聊吧{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真的吗？（现在的队伍将解散，组成和#tg两人的队伍）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好开心{。}，#pc！ 我真的很幸福{。}。</t>
   </si>
   <si>
     <t xml:space="preserve">好闲啊{。}。
@@ -3089,7 +3229,7 @@
 不要小看投石战士扔的石头{。}。
 在梦中能见到神吗{。}？
 好像有些在收集怪东西的贵族。{。}。
-在聚会上演奏的时候，喝醉的客人偶尔会扔些奇怪的东西{。}。
+在派对上演奏的时候，喝醉的客人偶尔会扔些奇怪的东西{。}。
 盗贼团的人好像经常使用什么奇怪的药{。}。
 旅行的魔法师用火焰的魔法给{我}烤肉了{。}。说实话，比店里的卖的都好吃{。}！
 挖不动岩石？试着用更硬的材料做镐子怎么样{。}？
@@ -3158,6 +3298,30 @@
 {我}能帮上什么忙吗？</t>
   </si>
   <si>
+    <t xml:space="preserve">露西亚|不归的船|当有人拿到这个瓶子的时候，我应该已经葬身海底了。不过天空真的很蓝。
+无名的士兵|最后的信|比剑更沉重的是恐惧。尽管如此我也希望有人知道，我没有逃跑。
+埃尔内斯|海潮的祈祷|神啊，如果没有平息波涛的力量，请至少给与我安眠。
+米蕾耶|约定的海滨|我先到的话就点燃篝火等你，可不要走错哦。
+领航员达罗斯|星的记录|今天星像也是正确的。出错的是我。
+塞雷娜|小小的告白|我只有一个遗憾，那就是没能唤出你的名字。
+老人|年轻时的日子|大海虽然会掠夺，但并不是一切都毫无意义。活下去。
+双胞胎妹妹|一半的世界|哥哥，世界还剩下一半呢。所以回来吧。
+船医雷纳特|医疗记录|我没能治好伤口，但让疼痛缓和了。这就足够了。
+伊莎贝尔|歌的后续|即使我不在了，也请把这首歌唱到最后。
+走私者凯尔|报酬的行踪|钱被沉入了北方的海湾。想要就去捞吧。
+见习神官罗亚|疑惑的告白|祈祷没有传达到。即使如此我也不会停止祈祷。
+渔夫哈尔德|最后的渔猎|今天没有渔获。但是和大海说了话。
+旅人希安|途经点|这里并不是终点。只是途经之处。
+王国书记官|官方记录摘抄|该船因风暴失事。报告结束。
+母亲|给孩子|记得天冷时要穿好外套。
+吟游诗人费伊|未完成的诗歌|韵律还是不行。致续写者。
+雇佣兵团长沃尔克|撤退命令|活着回去。名誉以后捡回来就行了。
+少女|第一次旅行|有点害怕。但是很开心。
+某人|给捡到的你|如果你读到了这个，证明世界还在延续。
+不明|我…|我要…回家…！
+不明|已经…|已经不行噗</t>
+  </si>
+  <si>
     <t xml:space="preserve">在米西利亚，人类和艾莱亚生活的很和睦{。}。
 在十年战争中，这个国家承受了很大的损害{。}。
 乔南公的继承人埃夫隆德大人，基本没什么好传闻啊{。}。
@@ -3279,6 +3443,13 @@
 #race啊，在你面前的是活了一千年以上的流放者{。}。</t>
   </si>
   <si>
+    <t xml:space="preserve">……哔？
+…………哔哔
+哔………
+…哔波………
+……哔……错误……</t>
+  </si>
+  <si>
     <t xml:space="preserve">这是什么地方？
 所谓的神，不过是比人类稍强，却又更加傲慢的家伙罢了。
 人类的行为，常常会因为感情的影响而出现执行错误。
@@ -3343,7 +3514,7 @@
 真是麻烦，我们急迫的行程被昏倒的冒险者耽误了。
 …别摆出这么一副看到稀奇存在的表情呀。如你所见，我们是被你们称为「异形」森林的居民。
 踏出森林的艾莱亚不再会被森林接纳。当然，我和拉纳莱是特例。毕竟与人类打交道是「使者」的职责所在。
-拉纳莱是继承了特殊血统的艾莱亚。诶呀，让她听到就会被唠叨了，这个话题还是到此为止吧！</t>
+拉纳莱是继承了特殊血统的艾莱亚。哎呀，让她听到就会被唠叨了，这个话题还是到此为止吧！</t>
   </si>
   <si>
     <t xml:space="preserve">少主作为帕罗米亚的继承人，希望他能更有操守一些。
@@ -4049,9 +4220,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>278280</xdr:colOff>
+      <xdr:colOff>275760</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>117000</xdr:rowOff>
+      <xdr:rowOff>114480</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4061,7 +4232,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49657680" cy="117000"/>
+          <a:ext cx="49655160" cy="114480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4199,7 +4370,7 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8"/>
   <cols>
     <col min="1" max="1" width="19.11" style="1" customWidth="1"/>
@@ -4230,7 +4401,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -4244,7 +4415,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>487</v>
+        <v>511</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
@@ -4258,7 +4429,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
@@ -4272,7 +4443,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -4286,7 +4457,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
@@ -4300,7 +4471,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -4314,7 +4485,7 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>492</v>
+        <v>516</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>23</v>
@@ -4328,7 +4499,7 @@
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>26</v>
@@ -4342,7 +4513,7 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -4356,7 +4527,7 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -4370,7 +4541,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>35</v>
@@ -4384,7 +4555,7 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>497</v>
+        <v>521</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>38</v>
@@ -4398,7 +4569,7 @@
         <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
@@ -4412,7 +4583,7 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>44</v>
@@ -4426,7 +4597,7 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>47</v>
@@ -4440,7 +4611,7 @@
         <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>501</v>
+        <v>525</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>50</v>
@@ -4454,7 +4625,7 @@
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>53</v>
@@ -4468,7 +4639,7 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>56</v>
@@ -4482,7 +4653,7 @@
         <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>59</v>
@@ -4496,7 +4667,7 @@
         <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>62</v>
@@ -4510,7 +4681,7 @@
         <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>65</v>
@@ -4524,7 +4695,7 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>68</v>
@@ -4538,7 +4709,7 @@
         <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>71</v>
@@ -4552,7 +4723,7 @@
         <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>74</v>
@@ -4566,7 +4737,7 @@
         <v>76</v>
       </c>
       <c r="B29" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>77</v>
@@ -4580,7 +4751,7 @@
         <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>80</v>
@@ -4594,7 +4765,7 @@
         <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>83</v>
@@ -4608,7 +4779,7 @@
         <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>86</v>
@@ -4622,7 +4793,7 @@
         <v>88</v>
       </c>
       <c r="B33" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>89</v>
@@ -4636,7 +4807,7 @@
         <v>91</v>
       </c>
       <c r="B34" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
@@ -4650,7 +4821,7 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>77</v>
@@ -4664,7 +4835,7 @@
         <v>95</v>
       </c>
       <c r="B36" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>80</v>
@@ -4678,7 +4849,7 @@
         <v>96</v>
       </c>
       <c r="B37" t="s">
-        <v>517</v>
+        <v>541</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>97</v>
@@ -4692,7 +4863,7 @@
         <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>100</v>
@@ -4706,7 +4877,7 @@
         <v>102</v>
       </c>
       <c r="B39" t="s">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>103</v>
@@ -4720,7 +4891,7 @@
         <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>106</v>
@@ -4734,7 +4905,7 @@
         <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>521</v>
+        <v>545</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>109</v>
@@ -4748,9 +4919,9 @@
         <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>522</v>
-      </c>
-      <c r="C42" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -4762,7 +4933,7 @@
         <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>115</v>
@@ -4776,7 +4947,7 @@
         <v>117</v>
       </c>
       <c r="B44" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>118</v>
@@ -4790,7 +4961,7 @@
         <v>120</v>
       </c>
       <c r="B45" t="s">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>121</v>
@@ -4804,7 +4975,7 @@
         <v>123</v>
       </c>
       <c r="B46" t="s">
-        <v>526</v>
+        <v>550</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>124</v>
@@ -4818,7 +4989,7 @@
         <v>126</v>
       </c>
       <c r="B47" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>127</v>
@@ -4832,7 +5003,7 @@
         <v>129</v>
       </c>
       <c r="B48" t="s">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>130</v>
@@ -4846,35 +5017,35 @@
         <v>132</v>
       </c>
       <c r="B49" t="s">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="50" ht="22.35">
+    <row r="50" ht="12.8">
       <c r="A50" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B50" t="s">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="51" ht="12.8">
+    <row r="51" ht="22.35">
       <c r="A51" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B51" t="s">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>139</v>
@@ -4888,7 +5059,7 @@
         <v>141</v>
       </c>
       <c r="B52" t="s">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>142</v>
@@ -4902,7 +5073,7 @@
         <v>144</v>
       </c>
       <c r="B53" t="s">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>145</v>
@@ -4911,12 +5082,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" ht="20.1" customHeight="1">
+    <row r="54" ht="12.8">
       <c r="A54" s="1" t="s">
         <v>147</v>
       </c>
       <c r="B54" t="s">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>148</v>
@@ -4930,7 +5101,7 @@
         <v>150</v>
       </c>
       <c r="B55" t="s">
-        <v>535</v>
+        <v>559</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>151</v>
@@ -4939,12 +5110,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" ht="22.35">
+    <row r="56" ht="20.1" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>153</v>
       </c>
       <c r="B56" t="s">
-        <v>536</v>
+        <v>560</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>154</v>
@@ -4953,12 +5124,12 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" ht="12.8">
+    <row r="57" ht="22.35">
       <c r="A57" s="1" t="s">
         <v>156</v>
       </c>
       <c r="B57" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>157</v>
@@ -4972,7 +5143,7 @@
         <v>159</v>
       </c>
       <c r="B58" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>160</v>
@@ -4986,12 +5157,12 @@
         <v>162</v>
       </c>
       <c r="B59" t="s">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="1" t="s">
         <v>164</v>
       </c>
     </row>
@@ -5000,12 +5171,12 @@
         <v>165</v>
       </c>
       <c r="B60" t="s">
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="4" t="s">
         <v>167</v>
       </c>
     </row>
@@ -5014,7 +5185,7 @@
         <v>168</v>
       </c>
       <c r="B61" t="s">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>169</v>
@@ -5028,12 +5199,12 @@
         <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>542</v>
+        <v>566</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -5042,12 +5213,12 @@
         <v>174</v>
       </c>
       <c r="B63" t="s">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="3" t="s">
         <v>176</v>
       </c>
     </row>
@@ -5056,12 +5227,12 @@
         <v>177</v>
       </c>
       <c r="B64" t="s">
-        <v>544</v>
+        <v>568</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="4" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5070,7 +5241,7 @@
         <v>180</v>
       </c>
       <c r="B65" t="s">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>181</v>
@@ -5084,7 +5255,7 @@
         <v>183</v>
       </c>
       <c r="B66" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>184</v>
@@ -5098,7 +5269,7 @@
         <v>186</v>
       </c>
       <c r="B67" t="s">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>187</v>
@@ -5112,21 +5283,21 @@
         <v>189</v>
       </c>
       <c r="B68" t="s">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="69" ht="12.8">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B69" t="s">
-        <v>549</v>
+        <v>573</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>193</v>
@@ -5135,12 +5306,12 @@
         <v>194</v>
       </c>
     </row>
-    <row r="70" ht="32.8">
-      <c r="A70" s="1" t="s">
+    <row r="70" ht="12.8">
+      <c r="A70" s="3" t="s">
         <v>195</v>
       </c>
       <c r="B70" t="s">
-        <v>550</v>
+        <v>574</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>196</v>
@@ -5154,7 +5325,7 @@
         <v>198</v>
       </c>
       <c r="B71" t="s">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>199</v>
@@ -5163,17 +5334,17 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" ht="12.8">
+    <row r="72" ht="32.8">
       <c r="A72" s="1" t="s">
         <v>201</v>
       </c>
       <c r="B72" t="s">
-        <v>552</v>
-      </c>
-      <c r="C72" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="3" t="s">
         <v>203</v>
       </c>
     </row>
@@ -5182,7 +5353,7 @@
         <v>204</v>
       </c>
       <c r="B73" t="s">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>205</v>
@@ -5196,12 +5367,12 @@
         <v>207</v>
       </c>
       <c r="B74" t="s">
-        <v>554</v>
-      </c>
-      <c r="C74" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="1" t="s">
         <v>209</v>
       </c>
     </row>
@@ -5210,7 +5381,7 @@
         <v>210</v>
       </c>
       <c r="B75" t="s">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>211</v>
@@ -5224,9 +5395,9 @@
         <v>213</v>
       </c>
       <c r="B76" t="s">
-        <v>556</v>
-      </c>
-      <c r="C76" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -5238,7 +5409,7 @@
         <v>216</v>
       </c>
       <c r="B77" t="s">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>217</v>
@@ -5247,26 +5418,26 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" ht="22.35">
+    <row r="78" ht="12.8">
       <c r="A78" s="1" t="s">
         <v>219</v>
       </c>
       <c r="B78" t="s">
-        <v>558</v>
-      </c>
-      <c r="C78" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="79" ht="12.8">
+    <row r="79" ht="22.35">
       <c r="A79" s="1" t="s">
         <v>222</v>
       </c>
       <c r="B79" t="s">
-        <v>559</v>
+        <v>583</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>223</v>
@@ -5280,9 +5451,9 @@
         <v>225</v>
       </c>
       <c r="B80" t="s">
-        <v>560</v>
-      </c>
-      <c r="C80" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>226</v>
       </c>
       <c r="D80" s="4" t="s">
@@ -5294,7 +5465,7 @@
         <v>228</v>
       </c>
       <c r="B81" t="s">
-        <v>561</v>
+        <v>585</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>229</v>
@@ -5308,13 +5479,97 @@
         <v>231</v>
       </c>
       <c r="B82" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>232</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="83" ht="12.8">
+      <c r="A83" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B83" t="s">
+        <v>587</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="84" ht="12.8">
+      <c r="A84" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B84" t="s">
+        <v>588</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="85" ht="12.8">
+      <c r="A85" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B85" t="s">
+        <v>589</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="86" ht="12.8">
+      <c r="A86" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B86" t="s">
+        <v>590</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="87" ht="12.8">
+      <c r="A87" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B87" t="s">
+        <v>591</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="88" ht="12.8">
+      <c r="A88" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B88" t="s">
+        <v>592</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -5334,7 +5589,7 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
   <cols>
     <col min="1" max="1" width="13.63" style="6" customWidth="1"/>
@@ -5368,269 +5623,283 @@
     </row>
     <row r="5" ht="74.6">
       <c r="A5" s="6" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" ht="43.25">
       <c r="A6" s="6" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B6" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" ht="43.25">
       <c r="A7" s="6" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B7" t="s">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" ht="43.25">
       <c r="A8" s="6" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="B8" t="s">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" ht="43.25">
       <c r="A9" s="6" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B9" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" ht="74.6">
       <c r="A10" s="6" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B10" t="s">
-        <v>568</v>
+        <v>598</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" ht="43.25">
       <c r="A11" s="6" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B11" t="s">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" ht="43.25">
       <c r="A12" s="6" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B12" t="s">
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" ht="95.5">
       <c r="A13" s="6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="B13" t="s">
-        <v>571</v>
+        <v>601</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" ht="32.8">
       <c r="A14" s="6" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B14" t="s">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" ht="32.8">
       <c r="A15" s="6" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="B15" t="s">
-        <v>573</v>
+        <v>603</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" ht="12.8">
       <c r="A16" s="6" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="B16" t="s">
-        <v>574</v>
+        <v>604</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" ht="22.35">
       <c r="A17" s="6" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B17" t="s">
-        <v>575</v>
+        <v>605</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" ht="22.35">
       <c r="A18" s="6" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B18" t="s">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" ht="200.7">
       <c r="A19" s="8" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" ht="168.65">
       <c r="A20" s="8" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="B20" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" ht="241.75">
       <c r="A21" s="6" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B21" t="s">
-        <v>579</v>
+        <v>609</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" ht="32.8">
       <c r="A22" s="6" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="B22" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" ht="22.35">
       <c r="A23" s="6" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B23" t="s">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>290</v>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" ht="231.3">
+      <c r="A24" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B24" t="s">
+        <v>612</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -5674,184 +5943,184 @@
     </row>
     <row r="5" ht="64.15">
       <c r="A5" s="1" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="B5" t="s">
-        <v>582</v>
+        <v>613</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" ht="53.7">
       <c r="A6" s="1" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="B6" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" ht="22.35">
       <c r="A7" s="1" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="B7" t="s">
-        <v>584</v>
+        <v>615</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" ht="64.15">
       <c r="A8" s="1" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="B8" t="s">
-        <v>585</v>
+        <v>616</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" ht="64.15">
       <c r="A9" s="1" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="B9" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" ht="95.5">
       <c r="A10" s="1" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="B10" t="s">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" ht="64.15">
       <c r="A11" s="1" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" ht="53.7">
       <c r="A12" s="1" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="B12" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" ht="74.6">
       <c r="A13" s="1" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="B13" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" ht="116.4">
       <c r="A14" s="3" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" ht="147.75">
       <c r="A15" s="3" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>592</v>
+        <v>623</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" ht="116.4">
       <c r="A16" s="3" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>593</v>
+        <v>624</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" ht="168.65">
       <c r="A17" s="3" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -5870,7 +6139,7 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
   <cols>
     <col min="1" max="1" width="14.58" style="1" customWidth="1"/>
@@ -5902,620 +6171,634 @@
     <row r="4" ht="12.8">
       <c r="C4" s="3"/>
     </row>
-    <row r="5" ht="126.85">
+    <row r="5" ht="53.7">
       <c r="A5" s="1" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="B5" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="6" ht="12.8">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" ht="126.85">
       <c r="A6" s="1" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="B6" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="7" ht="126.85">
-      <c r="A7" s="9" t="s">
-        <v>336</v>
+        <v>355</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" ht="12.8">
+      <c r="A7" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="B7" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="8" ht="105.95">
-      <c r="A8" s="1" t="s">
-        <v>339</v>
+        <v>358</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" ht="126.85">
+      <c r="A8" s="9" t="s">
+        <v>360</v>
       </c>
       <c r="B8" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" ht="105.95">
       <c r="A9" s="1" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="B9" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="10" ht="116.4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="10" ht="105.95">
       <c r="A10" s="1" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="B10" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="11" ht="43.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="11" ht="116.4">
       <c r="A11" s="1" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="B11" t="s">
-        <v>601</v>
+        <v>632</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="12" ht="32.8">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12" ht="43.25">
       <c r="A12" s="1" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="B12" t="s">
-        <v>602</v>
+        <v>633</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="13" ht="64.15">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="13" ht="32.8">
       <c r="A13" s="1" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="B13" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="14" ht="22.35">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" ht="64.15">
       <c r="A14" s="1" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="B14" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="15" ht="43.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="15" ht="22.35">
       <c r="A15" s="1" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="B15" t="s">
-        <v>605</v>
+        <v>636</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="16" ht="32.8">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="16" ht="43.25">
       <c r="A16" s="1" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="B16" t="s">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="17" ht="43.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" ht="32.8">
       <c r="A17" s="1" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="B17" t="s">
-        <v>607</v>
+        <v>638</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="18" ht="53.7">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="18" ht="43.25">
       <c r="A18" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>608</v>
+        <v>390</v>
+      </c>
+      <c r="B18" t="s">
+        <v>639</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="19" ht="53.7">
       <c r="A19" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="B19" t="s">
-        <v>609</v>
+        <v>393</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>640</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="20" ht="43.25">
+        <v>394</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" ht="12.8">
       <c r="A20" s="1" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="B20" t="s">
-        <v>610</v>
+        <v>641</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="21" ht="32.8">
+        <v>397</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="21" ht="43.25">
       <c r="A21" s="1" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="B21" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" ht="32.8">
       <c r="A22" s="1" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="B22" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" ht="32.8">
       <c r="A23" s="1" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="B23" t="s">
-        <v>613</v>
+        <v>644</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="24" ht="44.75">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" ht="32.8">
       <c r="A24" s="1" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="B24" t="s">
-        <v>614</v>
+        <v>645</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="25" ht="32.8">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="25" ht="44.75">
       <c r="A25" s="1" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="B25" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="26" ht="56.7">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" ht="32.8">
       <c r="A26" s="1" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="B26" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="27" ht="79.1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="27" ht="56.7">
       <c r="A27" s="1" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="B27" t="s">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="28" ht="44.75">
+        <v>418</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" ht="79.1">
       <c r="A28" s="1" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="B28" t="s">
-        <v>618</v>
+        <v>649</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="29" ht="13.8">
+        <v>421</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="29" ht="44.75">
       <c r="A29" s="1" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="B29" t="s">
-        <v>619</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="30" ht="179.1">
+        <v>650</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="30" ht="13.8">
       <c r="A30" s="1" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="B30" t="s">
-        <v>620</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="31" ht="12.8">
-      <c r="A31" s="9" t="s">
-        <v>408</v>
+        <v>651</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="31" ht="179.1">
+      <c r="A31" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="B31" t="s">
-        <v>621</v>
+        <v>652</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" ht="13.8">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="32" ht="12.8">
       <c r="A32" s="9" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="B32" t="s">
-        <v>622</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="33" ht="91">
+        <v>653</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" ht="13.8">
       <c r="A33" s="9" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="B33" t="s">
-        <v>623</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="34" ht="12.8">
-      <c r="A34" s="1" t="s">
-        <v>416</v>
+        <v>654</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="34" ht="91">
+      <c r="A34" s="9" t="s">
+        <v>437</v>
       </c>
       <c r="B34" t="s">
-        <v>624</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="35" ht="105.95">
-      <c r="A35" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>625</v>
+        <v>655</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="35" ht="12.8">
+      <c r="A35" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B35" t="s">
+        <v>656</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="36" ht="126.85">
+        <v>441</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="36" ht="105.95">
       <c r="A36" s="3" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
     </row>
     <row r="37" ht="126.85">
       <c r="A37" s="3" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>627</v>
+        <v>658</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="38" ht="22.35">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="38" ht="126.85">
       <c r="A38" s="3" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>429</v>
+        <v>659</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>450</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="39" ht="74.6">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="39" ht="22.35">
       <c r="A39" s="3" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>432</v>
+        <v>660</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>453</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="40" ht="105.95">
-      <c r="A40" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="B40" t="s">
-        <v>630</v>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" ht="74.6">
+      <c r="A40" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>661</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
     </row>
     <row r="41" ht="105.95">
       <c r="A41" s="1" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="B41" t="s">
-        <v>631</v>
+        <v>662</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
     </row>
     <row r="42" ht="105.95">
-      <c r="A42" s="9" t="s">
-        <v>440</v>
+      <c r="A42" s="1" t="s">
+        <v>461</v>
       </c>
       <c r="B42" t="s">
-        <v>632</v>
+        <v>663</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" ht="105.95">
       <c r="A43" s="9" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="B43" t="s">
-        <v>633</v>
+        <v>664</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="44" ht="95.5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="44" ht="105.95">
       <c r="A44" s="9" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="B44" t="s">
-        <v>634</v>
+        <v>665</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="45" ht="116.4">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="45" ht="95.5">
       <c r="A45" s="9" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="B45" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="46" ht="105.95">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="46" ht="116.4">
       <c r="A46" s="9" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="B46" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
     </row>
     <row r="47" ht="105.95">
       <c r="A47" s="9" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="B47" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="48" ht="95.5">
-      <c r="A48" s="1" t="s">
-        <v>458</v>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="48" ht="105.95">
+      <c r="A48" s="9" t="s">
+        <v>479</v>
       </c>
       <c r="B48" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>460</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="49" ht="95.5">
+      <c r="A49" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B49" t="s">
+        <v>670</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -6568,114 +6851,114 @@
     </row>
     <row r="5" ht="32.8">
       <c r="A5" s="1" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="B5" t="s">
-        <v>639</v>
+        <v>671</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" ht="168.65">
       <c r="A6" s="1" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="B6" t="s">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" ht="220.85">
       <c r="A7" s="1" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="B7" t="s">
-        <v>641</v>
+        <v>673</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" ht="231.3">
       <c r="A8" s="1" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="B8" t="s">
-        <v>642</v>
+        <v>674</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" ht="210.4">
       <c r="A9" s="1" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="B9" t="s">
-        <v>643</v>
+        <v>675</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" ht="314.9">
       <c r="A10" s="1" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="B10" t="s">
-        <v>644</v>
+        <v>676</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" ht="112.65">
       <c r="A11" s="1" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="B11" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" ht="199.95">
       <c r="A12" s="9" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="B12" t="s">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/dialog.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/dialog.xlsx
@@ -3474,7 +3474,7 @@
 呼呵呵，还特意向咱打招呼，真是有礼貌啊。
 这世间最棒的就是猫了。
 客人们迟早会忘记这个庭院，回到原本的时空。
-所有的灵魂，都可在这个庭院得享安宁。
+所有的灵魂，都可在这个庭院中得享安宁。
 被邀请到这个庭院的诸位，都怀着永恒安宁的碎片离开了。
 呼呵呵，汝也看得见吗？那些灵魂就像漂浮在水面上的花瓣一样，漂浮在时间无法触及的寂静中。
 庭院会记得所有曾在那寂静中入睡的灵魂。
@@ -3559,7 +3559,7 @@
     <t xml:space="preserve">行商的生活很无忧无虑，但是待在住得很舒服的镇上也不错。说起来，卡普尔附近就不错。
 兽人商人很少见吗？在提里斯可能很难看到吧。
 我收集的商品西到海洋之国维利察，东至沙漠黄金乡尼萨。请慢慢看。
-不…这东西不是头饰。</t>
+不…这可不是头饰。</t>
   </si>
   <si>
     <t xml:space="preserve">我是代理市长诺拉。有什么事吗？</t>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/dialog.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/dialog.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="general" sheetId="1" r:id="rId3"/>
-    <sheet name="rumor" sheetId="2" r:id="rId4"/>
-    <sheet name="zone" sheetId="3" r:id="rId5"/>
-    <sheet name="unique" sheetId="4" r:id="rId6"/>
-    <sheet name="asmr" sheetId="5" r:id="rId7"/>
+    <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="rumor" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="zone" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="unique" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="asmr" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="524">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -791,6 +791,87 @@
   </si>
   <si>
     <t xml:space="preserve">I'm so happy, #pc! I'm truly happy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rob1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">見損なった{よ}！
+ひどい{よ}、やめて{くれ}！
+返り討ちにしてくれる{よ}。
+ごろつき風情に何ができるという{のだ}？
+やめて{くれ}。きっと後悔する{よ}。
+傭兵さんたち、このごろつきを追い払って{くれ}。
+ふん、この護衛の数が見えないの{か}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I misjudged you!
+Please, stop this!
+You'll regret coming after me.
+What makes you think a common thug can take me on?
+Please stop. You'll regret this.
+Mercenaries, drive this ruffian off.
+Hmph. Can't you see how many guards I have?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mama_yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ママだよ！
+{はい}、ママ{だ}～！
+ママはここにいる{のだ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mommy's here!
+Yes, I'm your mommy!
+Mommy is right here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mama_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シッシッ！
+ママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+気持ち悪い{よ}…
+え…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoo, shoo!
+I'm not your mom!
+What are you talking about...?
+How pitiful... did you hit your head?
+That’s creepy...
+Huh...? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">baby_yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ママー！
+私の…ママなの{か}？
+マ…ママ…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mommy!
+...You are my...mommy?
+Ma... mama...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baby_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">こんなのママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+え…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You're not my mommy!
+What are you talking about...?
+How pitiful... did you hit your head?
+Huh...? </t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -1043,7 +1124,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">依頼が難しいと感じたら、名声を売ってしまうのも一つの手段{だ}。</t>
@@ -1889,7 +1970,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">ああ、いとも愛らしく安穏としたミシリアの都の一日だ。ミシリアの民は皆、目を塞いでいるかどこかに置き忘れてしまったのだろう。
@@ -1923,7 +2004,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Ah, what a lovely and peaceful day in Mysilia. All the people here must have closed their eyes or left them somewhere.
@@ -1980,7 +2061,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">I served in the royal court of Zanan long ago, but, well, I screwed up.
@@ -2009,7 +2090,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">私の家は、森の民の守護者の役職を代々受け継いできた。エレア達にとって苦難の時代の今、この称号が名ばかりでないことを証明したいよ。もちろん、そんな機会が訪れないのが一番だが。
@@ -2052,7 +2133,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Obviously the empire is a threat. but Zanan, who conceals her real intentions carefully, also creeps me out.
@@ -2881,1092 +2962,6 @@
 …Did I do a good job, Master…?
 …Milk? B-but…</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">这里有热腾腾的饭菜！用餐的话需要#1奥伦{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好了，请慢用{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在为受伤或生病而烦恼吗？支付#1的奥伦话，马上就可以开始治疗{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">请不要乱动哦，马上就让{你}的身体恢复健康{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">背包中沉睡着未鉴定的物品？只要#1奥伦，就可以帮{你}全部鉴定{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{好}，请稍等一下，马上就开始鉴定{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好像没有需要鉴定的东西{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">需要#2块金块来扩展家园{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好，家园扩展完成{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">似乎无法扩展家园{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">现在，您向米西利亚支付的额外税金是#1{。}。想改变金额的话就告诉我{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{好}，您向米西利亚支付的额外税金变更为#1{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">现在您的账户里有#1奥伦的金币{。}。那么，您要存多少钱{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">现在您的账户里有#1奥伦的金币{。}。那么，您要取出多少钱{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{好}，确认您的钱已经存好了{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{好}，请取走您的钱{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好像没有用来会面的接待室{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看起来钱不够的样子{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{你}好像已经吃饱了{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{哇}，{你}愿意接受{我}的任务吗{。}？那就{拜托了}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{你}好像已经接了不少委托了呢。先去处理一下手头的委托吧{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">任务进展的顺利吗{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{哇}，委托顺利结束了吗！{谢谢}。这是约好的报酬{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{哇}，{我}也喜欢观鸟{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">要上了{。}！
-呜嘿嘿。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这样啊{。}，那请先付{我}#1奥伦{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦，汝的伙伴已经相当成熟了啊？ 在长久旅途期间培育出的牵绊，现在正要迎来绽放的时刻。咱倒是能帮汝一把…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼呵呵呵呵呵呵，绽放吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼呵呵，那就要看汝的诚意了。来试着取悦咱吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">身材不错嘛{。}。{好}，{我}买了{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好啊，先给{我}#1奥伦吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">怎么了{。}，#pc？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这好像是别人的遗失物{。}…算了，无所谓了{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{你}想让{我}成为{你}家的居民吗{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">很遗憾{。}，{我}还有其他事要做{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果{你}更有些魅力的话或许可以{。}。#newline(魅力需要#1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">给{我}把#1拿来吧{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{我}的兴趣是#1{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">喜欢的东西{。}？这个嘛，{我}对#1有兴趣{。}。顺便说一下，{我}最喜欢的东西是#2{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想买#2吗，客人您的品味不错啊{。}。价格是#1奥伦{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">从今天开始#1就是{你}的东西了{。}。请好好珍惜{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#1吗？{好}，{我}给{你}带路{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{你}在开玩笑吗{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">将盟约之石升级到等级#2需要#1。#3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{好}，这样一来此地就能进一步发展了{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{你}对投资感兴趣吗？{你}到现在为止合计投资#2奥伦，#zone现在正在募集#1奥伦的投资{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{谢谢}！通过{你}的投资，#zone将来一定会发展得更好{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{你}要投资吗{。}？需要#1奥伦扩大这家店的规模{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{谢谢}！这样生意就能做的更好了{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{哇}{你}把#1送来了吗！{谢谢}。这就是约定好的报酬{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{哇}，这确实是#1。这就给{你}与这东西相称的报酬。{谢谢}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嚯，{你}有小奖章吗？收集小奖章就是{我}的人生意义啊！{我}这有很多引以为豪的作品，要和{我}交换吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{我}可不和罪犯做买卖。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{啊哈哈}，你这样的正经冒险者干嘛找我{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{你}想找谁？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#tg沉默了…)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#tg抱住了{你})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真是个无药可救的变态{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">终于恢复正常了吗{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#tg同意了)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#tg委婉地拒绝了)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特意给{我}送来了遗失物吗{。}。{你}真是市民的模范{。}。{谢谢}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这附近有个叫做#1的地方{。}。有兴趣的话不如去探索一番，也许会有不小的收获{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">很可惜{。}，最近没什么有用的消息{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是想要跟{我}试试吗{。}？
-{你}认真的{。}？
-{你}是想找{我}的麻烦{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{好}，胆子不小{。}！
-这就对了{。}！
-{好}，让{我}见识一下{你}的力量吧{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什么{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{好}，今天开始我就是您的女仆{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{啊哈哈}，#brother，{你}很缺钱啊{。}？这样吧，用#1奥伦把{你}的名声卖给我{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{谢谢}，{我}会好好利用{你}的名声{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想要接受祝福{。}？{好}，把头低下来{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这把锁太复杂了{。}。不好意思{。}，你还是自己想办法吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你要帮我还钱吗…真是不好意思。那就先从小额的欠款账单开始处理吧。在纳税箱还过钱之后，就来向我报告吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这样啊…下一份账单也拜托你了。真是过意不去啊，等还清债务后，再来跟我聊聊吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欠款账单应该已经给你了。那是很重要的东西，可别弄丢了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这个嘛…我还没做好心理准备。不好意思，再稍微等等吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我不是告诉过你了吗？因为是重要的东西所以别弄丢了。 我再给你一张，这次要小心点啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的…我愿意。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好开心{。}。但必须要有婚礼许可证{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好开心{。}。但还是回到据点再慢慢聊吧{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真的吗？（现在的队伍将解散，组成和#tg两人的队伍）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好开心{。}，#pc！ 我真的很幸福{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好闲啊{。}。
-嗯？有什么事吗{。}？
-偶尔也想吃顿大餐啊{。}。
-永恒盟约…？{我}没听说过这个词{。}。
-想喝库莱姆酒，喝到醉醺醺{。}。
-猫为什么这么可爱呢{。}。
-#aka？…是谁啊{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{我}对经济有关的话题很感兴趣{。}。
-总之，在世上钱很重要啊{。}。
-有没有哪里掉了零钱啊{。}。
-白金币好难搞啊{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{我}喜欢讨论科学{。}。
-艾斯·泰尔是第七纪的文明{。}。该文明有着高度发达的科学{。}。
-艾斯·泰尔似乎认为魔法和科学是对立的{。}。
-据说在新王国耶鲁，机械人偶正在从事和人类一样的工作{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{我}喜欢去各种各样的地方旅行{。}。
-鲁米艾斯特作为艺术之城而闻名{。}。
-北提里斯有很多被称为奈菲亚的遗迹群，有很多遗迹和迷宫{。}。
-如果要去旅行的话，最好准备好充足的食物{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{我}对世界形势很感兴趣{。}。
-艾沃达纳是位于东大陆沙漠的强大帝国{。}。
-据说新王国耶鲁是由逃离帝国的奴隶们建立的{。}。
-总感觉泽纳恩被帝国的气息笼罩着{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">信仰比什么都重要{。}。
-如果没有神的存在，这个世界就没有意义了{。}。
-据说治愈女神头上的翅膀的羽毛，拥有治愈任何疑难杂症的力量{。}。
-据说偶尔出现的大地摇晃是因为欧巴德斯在睡觉时翻身导致的{。}。
-库米罗妮大人是神还是女神这件事，让{我}在意到晚上睡不着觉{。}！
-幸运女神的真身其实是猫？{啊哈哈}，怎么可能有那样的事{。}！
-据传闻，机械之玛尼原本是人类{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在十年战争中，艾莱亚人对濒临危机的我们见死不救{。}。
-今后是人类的时代{。}！
-我们已经不需要艾莱亚人的帮助了{。}。
-艾莱亚人居住的森林，全部烧掉算了{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人类必须更加谦虚。应该向古老的种族充满敬意{。}。
-曾经，人类把艾莱亚称为母亲{。}。
-森林里的住民，似乎既不想干涉外界，也不希望被外界干涉{。}。
-为什么一定要去打扰森林住民的平静呢{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎光临。请慢慢看{。}。
-{我}这的货很全的{。}。
-经营一个店铺还是很难的{。}。
-如果不强大到能赶走流氓，就没资格当店主{。}。
-到其他商店卖东西可是会被压价的，{你}可要注意一下{。}。
-为了以防万一，{我}已经决定了店铺的继承人{。}。
-来，见识{我}引以为豪的商品吧{。}。
-最近不安分的家伙很多，很麻烦啊{。}。
-武器和防具如果没有好好鉴定，{我}就不能出高价收了{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保护市民的安全是守卫的工作{。}。
-看到可疑的人就向{我}报告{。}。
-{我}以前和{你}一样是个冒险者，直到…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">客人的钱比什么都重要{。}。
-有些东西靠钱可买不到{。}。
-欢迎光临本店{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊～啦，{你}真是个好#gender人{。}。让{我}送{你}一夜好梦吧{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这位客人也不是什么好人啊{。}。
-嘻嘻嘻…老板您真是个色鬼{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(感到无聊地看着{你})
-(#me瞥了{你}一眼，就转过身去)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">兔子的尾巴好像能呼唤幸运{。}。
-不要小看投石战士扔的石头{。}。
-在梦中能见到神吗{。}？
-好像有些在收集怪东西的贵族。{。}。
-在派对上演奏的时候，喝醉的客人偶尔会扔些奇怪的东西{。}。
-盗贼团的人好像经常使用什么奇怪的药{。}。
-旅行的魔法师用火焰的魔法给{我}烤肉了{。}。说实话，比店里的卖的都好吃{。}！
-挖不动岩石？试着用更硬的材料做镐子怎么样{。}？
-在这片大陆的某个地方，好像有居住着妖精的大树{。}。
-不交税的话会出大事的{。}。
-相信{我}！{我}看到了金色的雪波球{。}！
-据说有不可思议的灯能发出太阳光{。}。
-钓到大鱼就那样直接卖掉太可惜了{。}。
-知道吗？肚子饿了之后能吸收更多的营养{。}。
-如果想收集草药的话，可以去探索森林奈菲亚{。}。
-锻炼游泳就能增强耐力{。}！
-如果是美食家的话，好像能辨别蘑菇是否有毒{。}。
-锁住的宝箱，带到情报商那里就可以打开{。}。
-如果觉得委托很难的话，卖掉名声也是一种应对手段{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果{你}信仰库米罗妮，就可以从腐烂的食物中取出种子。
-不要把材质锤用在普通的装备上！
-高营养料理的真正功效会在喂宠物吃的时候发挥出来。
-在高质量的床上睡觉的话睡眠的效果会提高哦。
-对眩晕的敌人攻击能高概率打出会心一击。
-在毒、麻痹、出血等异常状态下，自愈将变得无效化。
-立方体在有异常状态时不会增殖。
-如果对古遗物使用重组卷轴，则可以让它重新生成。
-如果有足够的音抗性的话可以防止眩晕。
-有足够的幻惑抗性可以防止疯狂。
-祝福魔杖是个好主意，但据说效果比祝福的药水和卷轴稍差一些。
-湿的时候几乎不会受到火焰属性的伤害。但是受到电击属性的伤害会增加。
-短时间内吐太多会得厌食症。得了这种病只能喝东西充饥。
-被祝福的能力复苏药水和精神复苏药水，能够强化肉体和精神。
-可以向强敌投掷被诅咒的能力复苏药水和精神复苏药水。
-如果有游泳技能，就可以游到其他大陆去。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">听说有个很棒的戒指能增加{你}的手指。
-法杖放在地上一段时间就可以充能了！
-不知道该许什么愿？{你}可以试试许愿阿斯路的秘宝。
-宝石可以换成白金币。
-宝藏地图一定要祝福之后再读。
-喵…啊…啊啊…
-{你}的愿望是？
-在聊天窗口中喊出Guards！，守卫或许就会来帮忙哦。
-据说有一种方法可以让神成为宠物。
-在月门的前方等待着的是玩家杀手。
-{你}读了啊。读到这段文字的人*必定*会遭诅咒。
-{你}后面！小心！喂，快看，是妹—！快逃—！啊—！
-对{你}喵嘟噗喵嘟噗。
-由于您的存档文件损坏，无法正确显示幸运签。
-据说一猫不杀就会有好事发生。
-守卫好像很高兴被人裸体撞击。
-好像有妹妹专用的最强古遗物。
-在特尔斐附近建立牧场的话，马上就能成为有钱人了！
-如果善恶值高的话，可以让税金打折。
-怪物的粪便越重越能卖高价。
-喝被诅咒的恢复药水有时会生病。
-赫尔墨斯之血*一定要*祝福之后再喝！
-如果弄错了归还地点的话可能会很麻烦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果是办手续的话，请找秘书{。}。
-有什么事{。}？{我}很忙{。}。
-随时欢迎{你}投资城镇{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">来给城镇做些投资怎么样？
-{我}能帮上什么忙吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">露西亚|不归的船|当有人拿到这个瓶子的时候，我应该已经葬身海底了。不过天空真的很蓝。
-无名的士兵|最后的信|比剑更沉重的是恐惧。尽管如此我也希望有人知道，我没有逃跑。
-埃尔内斯|海潮的祈祷|神啊，如果没有平息波涛的力量，请至少给与我安眠。
-米蕾耶|约定的海滨|我先到的话就点燃篝火等你，可不要走错哦。
-领航员达罗斯|星的记录|今天星像也是正确的。出错的是我。
-塞雷娜|小小的告白|我只有一个遗憾，那就是没能唤出你的名字。
-老人|年轻时的日子|大海虽然会掠夺，但并不是一切都毫无意义。活下去。
-双胞胎妹妹|一半的世界|哥哥，世界还剩下一半呢。所以回来吧。
-船医雷纳特|医疗记录|我没能治好伤口，但让疼痛缓和了。这就足够了。
-伊莎贝尔|歌的后续|即使我不在了，也请把这首歌唱到最后。
-走私者凯尔|报酬的行踪|钱被沉入了北方的海湾。想要就去捞吧。
-见习神官罗亚|疑惑的告白|祈祷没有传达到。即使如此我也不会停止祈祷。
-渔夫哈尔德|最后的渔猎|今天没有渔获。但是和大海说了话。
-旅人希安|途经点|这里并不是终点。只是途经之处。
-王国书记官|官方记录摘抄|该船因风暴失事。报告结束。
-母亲|给孩子|记得天冷时要穿好外套。
-吟游诗人费伊|未完成的诗歌|韵律还是不行。致续写者。
-雇佣兵团长沃尔克|撤退命令|活着回去。名誉以后捡回来就行了。
-少女|第一次旅行|有点害怕。但是很开心。
-某人|给捡到的你|如果你读到了这个，证明世界还在延续。
-不明|我…|我要…回家…！
-不明|已经…|已经不行噗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在米西利亚，人类和艾莱亚生活的很和睦{。}。
-在十年战争中，这个国家承受了很大的损害{。}。
-乔南公的继承人埃夫隆德大人，基本没什么好传闻啊{。}。
-十年战争之后，这个国家被神秘的瘟疫袭击了{。}。有一种说法是，是尼米尔的奇迹之风，让疾病蔓延开来{。}。
-米西利亚今后会变成什么样呢{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎来到葡萄酒，温泉与樱花之村奥尔维纳。
-西奥露西亚真的对学习很热心，令人钦佩{。}。
-今年也满怀期待地等着湿衣大赛{。}！
-{我}想被法利斯狠狠地骂一顿{。}。
-奥尔维纳是米西利亚首屈一指的观光景点{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自从芙莉亚乌涅大人去世后，赛特拉斯大人就不怎么笑了{。}。
-虽然现在大家都把这个城堡叫做柳木堡{。}，但据说它以前有其他的名字{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎来到无法无天之人的城镇特尔斐。
-如果对那行当感兴趣的话，去盗贼公会就好了{。}。
-奴隶在这世上可是不可或缺的{。}。
-{我}就喜欢去竞技场见血{。}。
-这镇上没有守卫{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎来到帕罗米亚的王都。
-帕罗米亚什么都有，方便是方便{。}，但是实在太大了找人的时候会很辛苦{。}。
-贾比大人和斯塔莎大人的关系真的很好{。}。
-说起帕罗米亚名产，就是贵族的玩具{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这小村子的名字叫约恩{。}。
-如果需要马的话，在这里买就好了{。}。
-收获季总是人手不够{。}。
-村子算不上好，{你}随意慢慢逛吧{。}。
-听说西边有个犯罪者的城镇{。}。
-出了村子，沿着东边的路走就是王都帕罗米亚{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎来到水和艺术之城。
-听说有以温泉闻名的镇子{。}。
-在这城里，哪里都可以钓鱼{。}。
-绘画的话题烦死啦{。}。
-在帕罗米亚，只有这个城里有魔法师公会{。}。
-下水道味道很重，而且听说里面有可怕的怪物{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊嚏！嗯，今天也很冷{。}。
-每天都得铲雪真要命{。}。
-如果不能忍受罪恶感的话，去教会比较好{。}。
-好冷啊！
-{我}看到往南走一点的地方建了一个小工坊{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海风散发着清香{。}。
-{我}的兴趣是在宠物竞技场观看比赛{。}。
-如果想变得更强的话，去战士公会就好了{。}。
-这里的海产品在内陆地区卖得很好{。}。
-怎样才能进入金字塔呢{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我们种了很多米，会卖给人类一些{。}。
-吉须阿弥大人是这个村子的守护神{。}。
-这个村子的河是从莱娜村附近的山上流出来的{。}。
-我们的祖先就是在这座山的山丘上开辟了梯田种起了稻子{。}。
-村里的人都懂书法{。}。
-如果{你}对书法感兴趣的话，可以在杂货店买到书法工具{。}。
-如果在田地旁边看到了金色的鬼火，请马上通知姬奴。那是会迷惑人的邪恶之灵{。}。
-这个村子里种着许多萝卜啊葱啊等等蔬菜{。}。
-姬奴真的很擅长培育大米{。}。
-只有信仰吉须阿弥大人的人，才能感受到这个村子的灵力{。}。
-前往莱娜村的旅人，都会在挑战山路前在这个村子的旅馆休息一下{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我害怕走出村子。因为人类会若无其事地摸我的耳朵和尾巴{。}。
-穗罗女大人守护着这个村子的大家{。}。
-我讨厌那些会破坏村子气氛的游客{。}。
-相传晚上一个人在樱花树旁边，就能看到金色的九尾狐{。}。
-这个村子的人从小就学习剑术{。}。
-这个村子里卖的奶是最棒的{。}！
-米芙会从南方进回稻子来在这里酿酒{。}。
-樱花酒是献给女神的最好供品{。}。
-美佐岐的身体真的很丰韵。又大又有包容力，最棒了{。}！
-多亏了美佐岐和美珠奈，这个村庄才能安全又繁荣{。}。
-这个村子在北地来说算是比较温暖的地方。神木在冬天也不会落叶{。}。
-樱花酒是这个村子的名产{。}。
-在瀑布下冥想可以让身体与心灵中的邪恶得到净化{。}。
-只有信仰穗罗女大人的人，才能看到这个村子真正的美丽{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">因为这里离城镇很远，所以几乎所有的物资都是从空中送来的{。}。
-斯普睿聚集着很多冒险者，他们会在挑战奈菲亚前互相组队{。}。
-斯普睿对于许多前往北提里斯荒野的冒险者来说，是最后的补给地点{。}。
-这附近有许多危险的奈菲亚{。}。
-据说这附近有着没有大使馆特别许可就无法探索的奈菲亚{。}。
-这个村子原本是妖精们居住的地方{。}。
-从冒险者们开始路经这里后，这个村子也变大了{。}。
-树上会不停地举行宴会，这就是我们从冒险者那里赚钱的方法{。}。
-斯普睿的创立者好像是穿着青色茄子服装的妖精{。}。
-多亏了妖精的魔法，这棵树不会因被人们居住而受到影响，仍能健康地成长着{。}。
-我们照顾树木，树木也保护我们{。}。 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">#race为什么来这个村子…？
-#race来这里做什么{。}？
-结界保护着这个村子，让这里不会受到怪物侵犯也不会被好奇的人盯上{。}。
-有时，我们需要从外面的世界获取研究材料{。}。
-对我来说很重要的人都早已去世，现在在外面的世界已经没有人记得我了{。}。
-我们打破了众神的禁忌，被施加了侍奉伟大之父的任务{。}。
-长老比切林似乎不太想提起自己已经活了多少岁月{。}。
-如果你能给我们带些尝起来不像灰的食物，大家都会很高兴的{。}。
-这个村子里几乎没什么食材{。}。
-我们不会迎来自然的死亡{。}。
-伟大之父认为我们的罪过都被偿付之时，就是我们被释放的日子{。}。
-我们所拥有的知识，如果传到外面的世界就太危险了{。}。
-伟大之父总是守护着我们。
-伟大之父监督着我们进行赎罪，这是无法逃脱的命运{。}。
-随着时间的流逝，我们已经没有什么物质层面上的追求了{。}。
-#race啊，在你面前的是活了一千年以上的流放者{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">……哔？
-…………哔哔
-哔………
-…哔波………
-……哔……错误……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是什么地方？
-所谓的神，不过是比人类稍强，却又更加傲慢的家伙罢了。
-人类的行为，常常会因为感情的影响而出现执行错误。
-机械会损坏该怪设计得有问题吧？
-机械迟早有一天会取代人类统治这个世界吧。
-我记得我创造的一切事物。无一例外。
-…我怎会承认神这种不合理的东西。
-为什么这里有两个我？
-真是个无聊的地方。这地方有两个我的情况除外…
-…你说这只手臂？ 当然是我自己换的。
-你说我觊觎神的宝座…？ 哼，真是可笑。我都想拆开你的脑袋看看了。
-…这里的猫出奇的多啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好奇怪，什么都想不起来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">塔内隆？ 噢，咱确实曾听到过有人这么称呼这个庭院。
-怎么，汝也想被咱宠爱么？ 
-时间在这里毫无意义。
-呵，汝是旅行至此，还是迷路至此？又或者是根本不知这里是哪里就随便闯了进来的笨蛋呢。
-呼呵呵，还特意向咱打招呼，真是有礼貌啊。
-这世间最棒的就是猫了。
-客人们迟早会忘记这个庭院，回到原本的时空。
-所有的灵魂，都可在这个庭院中得享安宁。
-被邀请到这个庭院的诸位，都怀着永恒安宁的碎片离开了。
-呼呵呵，汝也看得见吗？那些灵魂就像漂浮在水面上的花瓣一样，漂浮在时间无法触及的寂静中。
-庭院会记得所有曾在那寂静中入睡的灵魂。
-愿有朝一日能尽情抚摸幸运女神呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵，哥哥，你去哪里了？
-您好，旅行者。请好好享受在这里的时光吧。
-这里真是个和平的地方。待在这里仿佛都要忘记时间的存在了…
-我在去看戏剧的途中和哥哥走散了。到底发生了什么呢？
-其实哥哥和我都对戏剧没什么兴趣。只不过欣赏戏剧在泽纳恩来说可是一种身为贵族的修养呢。
-你知道吗…？ 亚尔蒂海特似乎有妖精哦？
-别看哥哥那样子，如果没有我的话他可是很邋遢的，呵呵。
-因为罗缇先生向演奏会场扔过石头，所以他被禁止入内了。
-我要是去给罗缇先生送些什么的话，他还是会像少年一样害羞呢。
-罗伊特尔…？ 不，我只认识罗缇先生…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，你听过那个变成野兽的王子的童话吗？
-我们是来自温戴尔之森的使者。
-为了谒见公正的贾比王，洗清森林和艾莱亚人民蒙受的不白之冤，我们正朝着王都帕罗米亚行进。
-艾索里亚大陆与提里斯大陆相隔一片汪洋，在提里斯北部的就是北提里斯。
-愿风加护于你。
-这里是哪里呢…？
-米西利亚？ 嗯，我知道。但米西利亚已经…
-我觉得人类…有点可怕。但也对他们很有兴趣。
-艾莱亚没有人类的大多数欲望。我们对占有、统治和争斗没有兴趣。至于这是不是好事，就另当别论了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看样子你好像不是北提里斯人呢。
-你在这个世界上会见识怎样的事情，又会留下怎样的足迹呢？
-看来我们迷路跑到了奇怪的地方啊。
-我们正在向帕罗米亚旅行的途中。
-你在说什么？ 现在是西埃尔历517年吧？
-开拓韦尔尼斯？ 你撞坏脑袋了吗？
-真巧呢。我照顾过和你很像的冒险者。
-真是麻烦，我们急迫的行程被昏倒的冒险者耽误了。
-…别摆出这么一副看到稀奇存在的表情呀。如你所见，我们是被你们称为「异形」森林的居民。
-踏出森林的艾莱亚不再会被森林接纳。当然，我和拉纳莱是特例。毕竟与人类打交道是「使者」的职责所在。
-拉纳莱是继承了特殊血统的艾莱亚。哎呀，让她听到就会被唠叨了，这个话题还是到此为止吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">少主作为帕罗米亚的继承人，希望他能更有操守一些。
-就因为有基尔巴德这样的人在，少主才会跟着瞎闹。
-斯塔莎公主在这个年纪举止就彬彬有礼，而且行事果断。简直就是宫廷的偶像！
-斯塔莎公主万岁！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我和米拉尔在小到拿不动锤子的时候就是孽缘搭档了。
-就连我也非常认可米拉尔的才能。但这个家伙居然放着客户的订单不管，一直做什么猫玩具，真是可悲啊。
-无聊啊。难道就没有让我那蒙灰待燃的工匠之心再能燃烧起来的大委托吗！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈！…你是什么人？
-以欧巴德斯之名，接近斯塔莎公主的臭虫我会全部消灭的，呼哈哈哈！
-公主万岁！
-我也想在15年前的战争中展现风采啊！
-呼哈哈！
-帮助弱者，粉碎邪恶！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">来米西利亚宫廷有什么事吗？
-我也老了。但现在还不是隐退的时候。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">冒险者在这里做什么？
-孤儿院会养护并教育没有父母的孩子。
-即使在这世道下，我也希望孩子们能健康地成长。
-教育很重要。这些没有任何后盾的孩子，总有一天也要找份糊口的工作才行。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的名字是斯兰。是为帕罗米亚效力之人。现在为了修行而在各地旅行。
-话说回来贵重的书籍很多呢。
-在暴风雪的日子里到达了这座孤城，这阵子要承蒙照顾了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦哦，是客人啊！来来，不用客气，和我的猫儿们尽情嬉戏吧。
-我和搭档在工房的商号问题上吵架了。如果他有一点品味的话，就不会想出「盖罗克米拉尔」这种怪名字了吧。
-今天吃什么好呢。最近琢磨猫的食谱比当铁匠还开心。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">行商的生活很无忧无虑，但是待在住得很舒服的镇上也不错。说起来，卡普尔附近就不错。
-兽人商人很少见吗？在提里斯可能很难看到吧。
-我收集的商品西到海洋之国维利察，东至沙漠黄金乡尼萨。请慢慢看。
-不…这可不是头饰。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我是代理市长诺拉。有什么事吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，您找我有什么事吗？
-帕罗米亚是历史悠久的提里斯大国。我很荣幸被这个王宫接纳。
-偶像…？…是异国语言吗？
-在王宫的粉丝……啊……大……大家对我都很好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我对历史和传承很感兴趣。
-法利斯姐姐一生气就很可怕。
-帕罗米亚的王宫图书馆里有很多藏书，真是好地方。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是冒险家吗？一定要给我讲讲你的各种故事。
-父亲太严厉了。什么事都要挨个唠叨，真麻烦。希望科内利安不会受到不好的影响…
-基尔巴德和科内利安是从小就是朋友。即使有主从关系，但他们的友谊不会改变。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你谁啊？
-这里不是冒险者之流该来的好地方。快给我离开。
-……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是什么东西？不要随便和我搭话。
-啊，真了不起，米西利亚之都又迎来安稳祥和的新一天了。米西利亚人民莫不是都瞎了眼，还是把眼珠子都丢了呢。
-一个个的脸上都摆着悠闲的表情呢，一群蠢货。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">请不要太靠近…埃夫隆德大人会生气的。
-异形之森？…我没有去过。住在米西利亚的艾莱亚都是「森林外」的艾莱亚。
-像这样看着花很容易犯困呢…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">要听首歌吗？
-我以前侍奉着泽纳恩的王室，但是，我搞砸了…
-现在米西利亚才是我的故乡。
-看见梅尔文那家伙了吗？我刚好想唱一首歌呢。
-我的妻子是米西利亚最美丽最聪明的人。我简直配不上她。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妹妹嫁到贝里希身边已经八年啦。时间过得真快。
-我家世世代代继承了森之民守护者的职务。在这个苦难时代，我想证明这个称号不仅仅是名字而已。当然，没有证明的机会才是最好的。
-我的搭档格里芬是野生的猫头鹰。当时它受了伤，是我给它治好了。后来被它缠上，现在它好像觉得我的肩膀就是它的栖木。
-妇女们缺乏节操真叫人为难。
-埃夫隆德大人身边的有个叫艾露米纳雷的女孩，那个女孩难道……不，也许我想多了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是什么人？
-虽然冒险者这名字听起来不错，但他们不就是一群不愿工作的流浪汉吗？
-帝国的威胁自不必说，一直小心隐藏着真实意图的泽纳恩也让人毛骨悚然呢。
-据说帕罗米亚的泽茵王是有名的君主，而他的儿子贾比王子则是个玩世不恭的公子哥。看来任何国家都会为继承人的问题烦恼啊！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妹和立方体，哪个可怕？虽然我觉得妹更可爱一些。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你好啊，渡鸦。有什么事吗。
-来喝杯茶吧，渡鸦。
-我是『探求者』…也被称为『异界来客』。如你所见，我是个隐士。我为了获取世界上所有的知识献出了一切。
-…不过，亏你能找到这么偏僻的地方来啊。
-…这座城是属于我的大图书馆，不过图书馆好像就该敞开大门迎接众人来访…所以我欢迎你的到来。
-任何人都有获取这世界上所有的知识的权力。你在此处自由行动即可。
-在这个世界的某个地方，好像有刻着伊尔瓦全部历史与真相的秘宝…。
-永恒盟约…？这么古老的故事你也知道啊。
-你好，渡鸦。借你的书有认真读吗？
-把知识留给后世是获得知识之人的义务。
-你好，渡鸦。你有见过我的朋友斯兰吗？
-…这个头盔？它是很美的野兽吧。它是我的老朋友。
-……遮住脸的理由？10年战争之后，艾莱亚一直抬不起头啊…。
-……朋友们都先一步踏上旅途…。
-好像有个追逐妹犬之馆幻觉的疯子。
-战争还会发生吗。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">怎么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你能听到风在用古老的语言低语吗？我为了学习风的故事，正在游历世界。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我讨厌那些小鬼。他们一直在说些奇怪的话，真是讨厌！
-别拿我和那些怪物混为一谈。
-爸爸回来之后，我要让爸爸再也不带我来这里！
-我爸爸是｢科学家｣。来到这个托儿所后…那个怪物女就拜托爸爸帮她做什么事，爸爸还说很快就能回来…
-爸爸很快就能回来的。
-就算求我，我也不会和那些小鬼玩的。
-那些小鬼真是的，有时候还会捡回来一些奇怪的东西呢。
-那个怪物女才不是我妈妈呢。谁看了也知道不是才对吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，你是来玩彩球抽奖的吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我们既是祝福，也是诅咒。换个角度看，弱小也是一种强大。
-没有死亡的生命，没有地狱的天堂，没有离别的相遇，没有悲伤的喜悦…这样的世界是不存在的。
-我作为福缘之圣女，肩负着每年引导村庄举行封印仪式的职责。
-吉须阿弥大人的祝福普济众生。那份力量是足以干涉世界，没有信仰的人也能够感受到。
-我们培育的稻子寄宿着丰富的灵力，是封印仪式上不可或缺之物。
-喻部是一个扭曲的负之神，他想要消除众神之间所有的争斗，试图把理想和平带给伊尔瓦。
-决定继承圣女身份的时候，我舍弃了以前的名字，自称「姬奴」。总有一天，我的某个女儿也会踏上同样的道路。
-夏无永驻，四季轮回，寒冬将至。祝福也不会永远持续，不幸亦然。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">喻部是一个邪恶的负之神，他操纵着众神的战争，企图统治伊尔瓦。
-我们会在神树广场上献上仪式之舞。
-穗罗女大人爱着所有的生命，甚至会给予那些没有信仰的人小小的祝福。
-作为金剑之圣女，我每年都要为封印仪式献上剑舞。
-樱花的花瓣像女神的眼泪一样飘落，在我们的心中刻下转瞬即逝的美。
-仪式用的刀剑在祭拜女神时起着重要的作用。
-穗罗女大人对孩子们都很慈爱，她会为大家族祝福。涅芙一族算不上什么成员众多的种族，其中的大家族都很受尊敬。
-我的刀是历代圣女代代相传的。
-金剑之圣女们都立志用此刀创造新的传说。
-女神教导我们力量和美并非是对立的。涅芙的剑舞便是这两者的结合。
-涅芙的村庄是为了保护神树而建造的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是冒险者吗？竟然来到这样的地方，真是好奇心太旺盛了。
-我主要负责守护这里。虽然很光荣...但有时候好无聊啊。
-耶万大人的教导会被认为是残酷的，但那也是源自于对凡人的厚爱与期待。
-我讨厌机器。因为它们不会流血。
-来试试身手怎么样？最近的争斗完全不够。
-比利先生如果没有那些刺的话...
-猫真是可爱的生物...
-我留恋于战场上的硝烟。可以带我去吗？
-这里的景色很美，但是生活很不方便。只有去北方的米芙村玩才算得上是偶尔的乐趣。
-如果你想挑战沉睡在这里的负之神，我是不会阻止的。我想耶万大人也会很高兴才是。
-以太是一种非常有趣的物质。无论好坏，都会左右今后人类的前途。
-不觉得摸初次见面的狐族很失礼吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这条项链？里面装的当然是米啦。因为我们村里没有种小麦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这家旅馆原本是为了迎接朝圣者而建造的，但是最近接待的游客也变多了。
-欢迎光临！要吃饭吗？还是洗澡？还是…？
-不知道为什么村子会突然变得很热闹，不过，忙起来的感觉也不坏！
-游客们总是不顾美佐岐的警告，太过靠近圣树，真让人头疼。真是的，一点敬畏之心都没有。
-我们虽然可以自给自足，但是如果不从米芙村运来食物的话，根本招待不了这么多游客。
-为什么人类对我们的耳朵和尾巴那么感兴趣呢？
-美佐岐负责守护神殿，我负责管理旅馆。这样看来好像没什么长老能做的事了呢！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你想知道我为何被制造出来吗？不想？猜你也不想。
-我梦到一个像家一样的地方，但我想不起来该如何回到那里。
-我醒来时就拿着这个武器。它可真重啊。这是拿来刺的？还是用来射击？应该都行吧。
-「你好！我是大家的偶像，机械人偶机利亚～！」…我还装有偶像模块吗？这是什么时候录的？
-据说机械之玛尼会向聆听虚无之人低语。如果是那个人的话，可能会知道我为什么被制造出来。
-*zzt* 记忆又故障了…我来这里要干什么来着？
-*beep* 现在正在进行定期维护。请再稍等一下。
-你说我是小号的魔像？怎么可能呢。
-错误？故障？才没有，那只是我的功能罢了。
-*盯着看*啧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">天蓝色的郁金香？我虽然去过很多地方，但是从没见过那种东西哦。
-最近好像有什么奇怪的新病在流行着……不知会不会长出角来呢～。
-如果惹恼了某些神明就可能会被降下古怪的诅咒，要小心哦。
-赌场的庄家绝对在｢出老千｣……！ 
-蛋的蛋♪刺身的刺身♪刺身的蛋♪
-人外有人，杂鱼外有杂鱼。#brother2是哪边呢？
-我本来还有另一根角……不对是刀，但在旅途中丢失了。
-享用美食的时刻最幸福♪
-牙姬酱驾到。快来招待一下啦。
-牙姬酱就是可爱又强大☆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你我的灵魂能够再次交织，不正意味着到了我们实现约定的时候吗…？ 
-若你就是我所寻求之人…那命运一定会轻轻向我们诉说吧。
-我能在你身上感受到一种好像已经在漫长时空中丢失的安宁感。
-你的灵魂让我感到如此熟悉…就仿佛在言语诞生之前，你我就已曾邂逅。
-若此刻能够永远持续下去就好了…我还想再多感受一下你的温暖。
-你只是一位温柔的陌生人吗…又或者真的是我跨越时空追寻的那道身影呢…
-我还是没法叫出现在就在我面前的…你的名字…
-真是不可思议…只要待在你身边，就会感觉十分安心。
-你也感觉到了吗…？那条连接着你我之间的命运之线？
-无论走过多少路…旅途的前方都一定会有你在。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你在意我是什么时候出生的吗#brother2？那是很久很久以前的故事了#brother2…
-我一直为了寻找#brother2而在这个世界上徘徊…然后就找到了#brother2！
-#brother2会和我永远……在一起吧…？我只是有点不安而已啦#brother2。
-为了#brother2，无论战斗还是家务，都要做好才行。
-神有时很残酷呢#brother2…
-我没有束缚#brother2哦！真的哦！
-我的歌声中似乎寄宿着混沌的力量。
-除了我以外这个世界上还有着许多和#brother2没有血缘关系的妹妹！
-好想摸雪波球！也想摸#brother2！
-雪波球有不同颜色的哦#brother2。如果能都带回家就好了#brother2。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我叫娜娜苏，是茄子妖精哦～。
-你问我喜欢的东西是什么？当然是茄子啦～。
-斯普睿是个非常好的地方哦~大家都在开心地跳舞呢～。
-冒险中得到宝物当然很开心，但最开心的是一起冒险得到的羁绊哦～。
-我经常和冒险途中遇到的新朋友一起喝酒。非常开心呢～。
-当然也发生过悲伤的事情，但我仍然相信今后还会有新的邂逅所以在不断前进，这就是现在的我～。
-虽然相遇总有一天会结束，但我觉得在那之中得到的东西绝对不是徒劳哦～。
-据说是一只青色茄子的妖精创建了斯普睿……希望我有朝一日能试着超越她呢～。
-其实我小时候曾和青色茄子的妖精对练过哦。她虽然是妖精，但是很强壮呢～。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我是莱伊娜！随便碰我的话会被电麻的！
-哎呀，冒险者。找我有什么事？
-和珀伊娜的关系？嗯～只是恶作剧伙伴而已？不过我们搭档冒险已经很久了。
-我并不讨厌娜娜苏哦？只是…想稍微捉弄一下，把她变成烤茄子！呀哈哈！
-我和珀伊娜、娜娜苏三个人第一次一起去冒险的时候，差点因为娜娜苏冒失死掉…多亏我机智才有了转机。真是的…
-虽然争夺包的时候我和娜娜苏是对手，但我偶尔也会和娜娜苏一起冒险哦。不过她基本都是负责去当诱饵啦！呀哈哈！
-包括我在内，最近斯普睿愿意去冒险的妖精变多了。不过竞争对手增加也不是什么坏事啦！
-…我发烧的时候，娜娜苏照顾过我。那时候的我无法好好向她道谢，但是我真的很感激。
-你问创立斯普睿的青色茄子妖精…？啊，她啊…以前我曾和她对练过，但是从没赢过！
-我本来还想着要从青色茄子妖精那扳回一局呢，但是不知什么时候她就离开了！…赢了就跑，真气人！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我是珀伊娜，你要是敢多说废话就毒死你。
-…怎么？有什么事么？
-莱伊娜有时候把战斗想得太简单。说了多少遍冒险不是玩游戏，真是个笨蛋…
-娜娜苏太天真了。她说她很重视羁绊，但总有一天她会被那羁绊绊倒的…
-我和莱伊娜也算认识很久了，我只把她当成是恶作剧的伙伴。不过我并不讨厌和她一起冒险。
-我更喜欢发动奇袭，但是莱伊娜总是会立刻冲锋陷阵造成无谓的消耗…太笨了…
-你听莱伊娜说过和娜娜苏第一次冒险的事吗？那时候娜娜苏让大家遭遇了危险，后来还哭了鼻子，哈哈。
-…以前有次我丢了东西，娜娜苏还拼命的帮我找。明明平时我总是对她搞恶作剧之类的…真是个笨蛋…
-我和娜娜苏还有莱伊娜曾经一起受过青色茄子的妖精的训练。但是我的毒攻击对她几乎没有效果。
-也不知现在的我加上莱伊娜还有娜娜苏能不能联手打赢青色茄子的妖精。只是她从很久以前就不知去向了…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪波球酱，真可爱啊……嘿嘿嘿……。
-真羡慕自由自在的猫咪。如果世上有猫咪的神明，那一定是自由的化身吧。
-明明只想平凡度日，为什么麻烦总是找上门呢……*叹气*
-我也不知道自己是怎么和那位说话方式奇奇怪怪的冒险者完成交流的……。
-那个可爱的人偶冒险者，一直在寻找着谁呢……。
-那位黑翼的冒险者，好帅啊……。
-那位法师冒险者，好像带着本危险的书呢……。
-那位相信命运引导的冒险者，总感觉很热情呢。
-听说有位吸……猫？的冒险者……？
-米西利亚的魔女面包师，真是太厉害了！既是魔女，又是面包师！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的料理中使用的都是顶级食材。
-想不想看看我的扫把收藏？
-嗯嗯…蝾螈的舌头…蜜蜂的眼睛。啊嗯？ 抱歉，没注意到你在这里。我正在思考新的食谱呢。
-咦，你有看到这附近有只猫吗？
-面包当然要用窑做呀？
-药品柜？  你给我好好看看，这是香料柜！
-我的帽子？　呵呵，很漂亮吧？
-（魔女把装满一袋的虫子哗啦一声都倒进了搅拌盆里。）
-……你的问题真多啊…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…哔—…
-…沙沙沙…
-…沙沙…嘎嘎…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…抚摸…抚摸…
-…抱抱…
-…紧抱…
-…乖…乖…
-…笨…笨蛋…
-…别…别误会了…
-…才…才不是…为了你呢…
-…才…才不是…
-…只…只是想打发无聊的时间罢了…
-…嗯…嘿咻…
-…被治愈吧…
-…呼…
-…咳…咳…
-…迷茫的…人们啊…
-…治…治愈…
-…受伤的…灵魂…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…嘎吱…嘎吱嘎吱…
-…轰轰轰轰……
-…咯吱咯吱……
-…垮拉……
-…轰隆…哗啦……
-…咔哩…咔哩咔哩……
-…轰……轰—……
-…咯吱…咯吱吱吱……
-…咔吧……嘎吧吧……
-…喳啦……喳啦喳啦……
-…咚……咚……
-…咣……咣……
-…咚……
-…呼哈哈哈哈哈哈哈……
-…呼哈哈……呼哈啊……
-…呼哈—……
-…呼……呼哈……
-@3呼哈哈哈哈哈哈哈！ 
-@3呼哈—
-…呼呼……
-…呼—…！ …呼—…！……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…别怕…妈妈会一直在你身边…
-…晚安…好孩子…
-…可以来…妈妈怀里哦…
-…只是好好活着…就很了不起了…
-…来…让我摸摸头…放心吧…
-…来…放松下来…
-…乖乖…
-…就这样…暖暖和和地…
-…摸摸…摸摸…力气，放松…
-…嗯…乖乖…好孩子…
-…就这样…暖暖的…
-…什么都…不用想了…
-…毛茸茸的…很安心吧…
-…用这尾巴…把你卷起来…
-…松松…软软…来…尾巴…
-…轻轻地…轻轻地…温柔…卷起…
-…温暖…温暖…你困了…
-…就这样…紧贴在一起…
-…吸…哈啊…一起…呼吸…
-…妈妈在哦…
-…摸摸…摸摸…力气，放松…
-…来…*紧紧抱住*…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…呵呵呵……
-…呵呵……
-…呵……呵呵呵……
-…呵呵……呵呵…
-…回去吧……
-…回到元素之中……
-…回归……
-…向元素之中……呵呵……
-…呵……呵……呵……
-…呵……呵……
-…呵呵……呵……
-…快……
-…呵呵呵呵……
-…呵呵呵呵呵……
-…呵呵……呵呵……呵呵……
-………
-………
-……猕猴桃……呵呵……
-……
-… </t>
-  </si>
-  <si>
-    <t xml:space="preserve">…哼…你喜欢这种的…？
-…真是个变态…
-…你这…蠢猪……啊哈哈……！
-…哎呀…在发抖呢……真可怜…
-…你喜欢…被看不起的感觉吧…？
-…区区蝼蚁……啊哈哈哈…
-…好小……真的……好小……
-…啊哈……真可笑……
-…啊哈哈……杂碎……真是杂碎……！
-…真可悲……
-…来…露出更多丑态吧…
-…在女神面前…真亏你能做出那种表情…
-…啊哈哈…可悲的猪猡…
-…那表情…真是…丢人至极…
-…快…给我趴在地上吧…
-…啊哈…连风都在嘲笑你…
-…谁允许你…直视女神了……？
-…再敢抬头的话…就把你剁成肉酱…
-…啊哈…可悲的凡人啊…
-…真是…好懂呢…
-…啊哈哈…没救的家伙…
-…丢人的家伙…挨了骂…还乐在其中…
-…这个…变态…
-…啊啊…刚才的…很让你开心吧…？
-…垃圾…
-…你就这样…毫无价值地存在下去吧…
-…你…该不会另有所图吧…？
-…啊啊…猜中了……啊哈哈！
-…光是存在就让人觉得…不舒服呢…啊哈…
-…真的是…无药可救的变态啊……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@3喵咪咪！
-@3帝王蟹！
-…蹭…
-…蹭蹭…
-…舔…
-…舔舔…
-…咚…
-…喵咪…
-…咪咪咪…
-…咪…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…早上好，主人…
-…这就为您奉上茶水…
-…您不在的时候，宅邸的事务我都管理好了…
-…家族中只有我的胸部这么小…不甘心…
-…梯子…放到哪里去了…？
-…啊…您脸上沾上东西了哦…
-…请让我代替主人…来处理吧…
-…我还要捣…多久年糕呢…？
-…呀啊！…
-…主、主人…！
-…照顾您是女仆的职责……但就算不是职责，我也会做的…
-…今天的晚餐…想吃点什么呢，主人…？
-…来，张…嘴…♥
-…我听说甲鱼…十分的滋补…
-…架子高处的东西，不用抱起我也可以拿得到哦…？
-…和主人靠得这么近…作为女仆，有点静不下心…
-…记得适当运动哦…？
-…我…做的好吗，主人…？
-…奶…奶吗…？ 但、但是……</t>
-  </si>
 </sst>
 </file>
 
@@ -3986,19 +2981,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -4012,7 +3007,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -4025,7 +3020,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -4051,7 +3046,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -4060,82 +3055,82 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4210,7 +3205,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4220,11 +3215,11 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>275760</xdr:colOff>
+      <xdr:colOff>274320</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>114480</xdr:rowOff>
+      <xdr:rowOff>113040</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="0" name="Rectangle 2" hidden="1"/>
         <xdr:cNvSpPr/>
@@ -4232,13 +3227,13 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49655160" cy="114480"/>
+          <a:ext cx="49653720" cy="113040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9360">
           <a:solidFill>
@@ -4366,20 +3361,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
-  <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8"/>
+  <dimension ref="A1:D93"/>
+  <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.11" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.41" style="1" customWidth="1"/>
-    <col min="3" max="3" width="95.53" style="1" customWidth="1"/>
-    <col min="4" max="4" width="86.34" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="95.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="86.34"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12" customHeight="1">
+    <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4393,16 +3388,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="12" customHeight="1"/>
-    <row r="3" ht="12" customHeight="1"/>
-    <row r="4" ht="12" customHeight="1"/>
-    <row r="5" ht="12" customHeight="1">
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>510</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
@@ -4410,13 +3402,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1">
+    <row r="6" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
-        <v>511</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
@@ -4424,13 +3413,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1">
+    <row r="7" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>512</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
@@ -4438,13 +3424,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1">
+    <row r="8" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>513</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
@@ -4452,13 +3435,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1">
+    <row r="9" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
-        <v>514</v>
-      </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
@@ -4466,13 +3446,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1">
+    <row r="10" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
-        <v>515</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
@@ -4480,13 +3457,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1">
+    <row r="11" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
-        <v>516</v>
-      </c>
       <c r="C11" s="1" t="s">
         <v>23</v>
       </c>
@@ -4494,13 +3468,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1">
+    <row r="12" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B12" t="s">
-        <v>517</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
@@ -4508,13 +3479,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1">
+    <row r="13" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B13" t="s">
-        <v>518</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
@@ -4522,13 +3490,10 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1">
+    <row r="14" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
-        <v>519</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
@@ -4536,13 +3501,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1">
+    <row r="15" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>520</v>
-      </c>
+      <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
         <v>35</v>
       </c>
@@ -4550,13 +3513,10 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1">
+    <row r="16" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B16" t="s">
-        <v>521</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>38</v>
       </c>
@@ -4564,13 +3524,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1">
+    <row r="17" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B17" t="s">
-        <v>522</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
@@ -4578,13 +3535,10 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1">
+    <row r="18" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B18" t="s">
-        <v>523</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>44</v>
       </c>
@@ -4592,13 +3546,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1">
+    <row r="19" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B19" t="s">
-        <v>524</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>47</v>
       </c>
@@ -4606,13 +3557,10 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1">
+    <row r="20" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B20" t="s">
-        <v>525</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>50</v>
       </c>
@@ -4620,13 +3568,10 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" ht="20.1" customHeight="1">
+    <row r="21" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B21" t="s">
-        <v>526</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>53</v>
       </c>
@@ -4634,13 +3579,10 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1">
+    <row r="22" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B22" t="s">
-        <v>527</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>56</v>
       </c>
@@ -4648,13 +3590,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1">
+    <row r="23" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B23" t="s">
-        <v>528</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>59</v>
       </c>
@@ -4662,13 +3601,10 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" ht="20.1" customHeight="1">
+    <row r="24" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B24" t="s">
-        <v>529</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>62</v>
       </c>
@@ -4676,13 +3612,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1">
+    <row r="25" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B25" t="s">
-        <v>530</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>65</v>
       </c>
@@ -4690,13 +3623,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" ht="20.1" customHeight="1">
+    <row r="26" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B26" t="s">
-        <v>531</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>68</v>
       </c>
@@ -4704,13 +3634,10 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" ht="20.1" customHeight="1">
+    <row r="27" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B27" t="s">
-        <v>532</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>71</v>
       </c>
@@ -4718,13 +3645,10 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" ht="20.1" customHeight="1">
+    <row r="28" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B28" t="s">
-        <v>533</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>74</v>
       </c>
@@ -4732,13 +3656,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" ht="20.1" customHeight="1">
+    <row r="29" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B29" t="s">
-        <v>534</v>
-      </c>
       <c r="C29" s="3" t="s">
         <v>77</v>
       </c>
@@ -4746,13 +3667,10 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" ht="20.1" customHeight="1">
+    <row r="30" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B30" t="s">
-        <v>535</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>80</v>
       </c>
@@ -4760,13 +3678,10 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" ht="20.1" customHeight="1">
+    <row r="31" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B31" t="s">
-        <v>536</v>
-      </c>
       <c r="C31" s="5" t="s">
         <v>83</v>
       </c>
@@ -4774,13 +3689,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" ht="20.1" customHeight="1">
+    <row r="32" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B32" t="s">
-        <v>537</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>86</v>
       </c>
@@ -4788,13 +3700,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" ht="20.1" customHeight="1">
+    <row r="33" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B33" t="s">
-        <v>538</v>
-      </c>
       <c r="C33" s="5" t="s">
         <v>89</v>
       </c>
@@ -4802,13 +3711,10 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B34" t="s">
-        <v>539</v>
-      </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
@@ -4816,13 +3722,10 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" ht="22.35">
+    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B35" t="s">
-        <v>534</v>
-      </c>
       <c r="C35" s="3" t="s">
         <v>77</v>
       </c>
@@ -4830,13 +3733,10 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B36" t="s">
-        <v>540</v>
-      </c>
       <c r="C36" s="1" t="s">
         <v>80</v>
       </c>
@@ -4844,13 +3744,10 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B37" t="s">
-        <v>541</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>97</v>
       </c>
@@ -4858,13 +3755,10 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B38" t="s">
-        <v>542</v>
-      </c>
       <c r="C38" s="1" t="s">
         <v>100</v>
       </c>
@@ -4872,13 +3766,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" ht="12.8">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B39" t="s">
-        <v>543</v>
-      </c>
       <c r="C39" s="1" t="s">
         <v>103</v>
       </c>
@@ -4886,13 +3777,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" ht="12.8">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B40" t="s">
-        <v>544</v>
-      </c>
       <c r="C40" s="1" t="s">
         <v>106</v>
       </c>
@@ -4900,13 +3788,10 @@
         <v>107</v>
       </c>
     </row>
-    <row r="41" ht="12.8">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B41" t="s">
-        <v>545</v>
-      </c>
       <c r="C41" s="1" t="s">
         <v>109</v>
       </c>
@@ -4914,13 +3799,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="42" ht="12.8">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B42" t="s">
-        <v>546</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>112</v>
       </c>
@@ -4928,13 +3810,10 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43" ht="12.8">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B43" t="s">
-        <v>547</v>
-      </c>
       <c r="C43" s="3" t="s">
         <v>115</v>
       </c>
@@ -4942,13 +3821,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" ht="12.8">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B44" t="s">
-        <v>548</v>
-      </c>
       <c r="C44" s="3" t="s">
         <v>118</v>
       </c>
@@ -4956,13 +3832,10 @@
         <v>119</v>
       </c>
     </row>
-    <row r="45" ht="12.8">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B45" t="s">
-        <v>549</v>
-      </c>
       <c r="C45" s="3" t="s">
         <v>121</v>
       </c>
@@ -4970,13 +3843,10 @@
         <v>122</v>
       </c>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B46" t="s">
-        <v>550</v>
-      </c>
       <c r="C46" s="3" t="s">
         <v>124</v>
       </c>
@@ -4984,13 +3854,10 @@
         <v>125</v>
       </c>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B47" t="s">
-        <v>551</v>
-      </c>
       <c r="C47" s="3" t="s">
         <v>127</v>
       </c>
@@ -4998,13 +3865,10 @@
         <v>128</v>
       </c>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B48" t="s">
-        <v>552</v>
-      </c>
       <c r="C48" s="3" t="s">
         <v>130</v>
       </c>
@@ -5012,13 +3876,10 @@
         <v>131</v>
       </c>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B49" t="s">
-        <v>553</v>
-      </c>
       <c r="C49" s="3" t="s">
         <v>133</v>
       </c>
@@ -5026,13 +3887,10 @@
         <v>134</v>
       </c>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B50" t="s">
-        <v>554</v>
-      </c>
       <c r="C50" s="3" t="s">
         <v>136</v>
       </c>
@@ -5040,13 +3898,10 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" ht="22.35">
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B51" t="s">
-        <v>555</v>
-      </c>
       <c r="C51" s="3" t="s">
         <v>139</v>
       </c>
@@ -5054,13 +3909,10 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" ht="12.8">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B52" t="s">
-        <v>556</v>
-      </c>
       <c r="C52" s="3" t="s">
         <v>142</v>
       </c>
@@ -5068,13 +3920,10 @@
         <v>143</v>
       </c>
     </row>
-    <row r="53" ht="12.8">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B53" t="s">
-        <v>557</v>
-      </c>
       <c r="C53" s="3" t="s">
         <v>145</v>
       </c>
@@ -5082,13 +3931,10 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" ht="12.8">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B54" t="s">
-        <v>558</v>
-      </c>
       <c r="C54" s="3" t="s">
         <v>148</v>
       </c>
@@ -5096,13 +3942,10 @@
         <v>149</v>
       </c>
     </row>
-    <row r="55" ht="20.1" customHeight="1">
+    <row r="55" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B55" t="s">
-        <v>559</v>
-      </c>
       <c r="C55" s="3" t="s">
         <v>151</v>
       </c>
@@ -5110,13 +3953,10 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" ht="20.1" customHeight="1">
+    <row r="56" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B56" t="s">
-        <v>560</v>
-      </c>
       <c r="C56" s="3" t="s">
         <v>154</v>
       </c>
@@ -5124,13 +3964,10 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" ht="22.35">
+    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B57" t="s">
-        <v>561</v>
-      </c>
       <c r="C57" s="3" t="s">
         <v>157</v>
       </c>
@@ -5138,13 +3975,10 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" ht="12.8">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B58" t="s">
-        <v>562</v>
-      </c>
       <c r="C58" s="3" t="s">
         <v>160</v>
       </c>
@@ -5152,13 +3986,10 @@
         <v>161</v>
       </c>
     </row>
-    <row r="59" ht="12.8">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B59" t="s">
-        <v>563</v>
-      </c>
       <c r="C59" s="3" t="s">
         <v>163</v>
       </c>
@@ -5166,13 +3997,10 @@
         <v>164</v>
       </c>
     </row>
-    <row r="60" ht="12.8">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B60" t="s">
-        <v>564</v>
-      </c>
       <c r="C60" s="3" t="s">
         <v>166</v>
       </c>
@@ -5180,13 +4008,10 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" ht="12.8">
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B61" t="s">
-        <v>565</v>
-      </c>
       <c r="C61" s="3" t="s">
         <v>169</v>
       </c>
@@ -5194,13 +4019,10 @@
         <v>170</v>
       </c>
     </row>
-    <row r="62" ht="12.8">
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B62" t="s">
-        <v>566</v>
-      </c>
       <c r="C62" s="3" t="s">
         <v>172</v>
       </c>
@@ -5208,13 +4030,10 @@
         <v>173</v>
       </c>
     </row>
-    <row r="63" ht="12.8">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B63" t="s">
-        <v>567</v>
-      </c>
       <c r="C63" s="3" t="s">
         <v>175</v>
       </c>
@@ -5222,13 +4041,10 @@
         <v>176</v>
       </c>
     </row>
-    <row r="64" ht="12.8">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B64" t="s">
-        <v>568</v>
-      </c>
       <c r="C64" s="3" t="s">
         <v>178</v>
       </c>
@@ -5236,13 +4052,10 @@
         <v>179</v>
       </c>
     </row>
-    <row r="65" ht="12.8">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B65" t="s">
-        <v>569</v>
-      </c>
       <c r="C65" s="3" t="s">
         <v>181</v>
       </c>
@@ -5250,13 +4063,10 @@
         <v>182</v>
       </c>
     </row>
-    <row r="66" ht="12.8">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B66" t="s">
-        <v>570</v>
-      </c>
       <c r="C66" s="3" t="s">
         <v>184</v>
       </c>
@@ -5264,13 +4074,10 @@
         <v>185</v>
       </c>
     </row>
-    <row r="67" ht="12.8">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B67" t="s">
-        <v>571</v>
-      </c>
       <c r="C67" s="3" t="s">
         <v>187</v>
       </c>
@@ -5278,13 +4085,10 @@
         <v>188</v>
       </c>
     </row>
-    <row r="68" ht="12.8">
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B68" t="s">
-        <v>572</v>
-      </c>
       <c r="C68" s="3" t="s">
         <v>190</v>
       </c>
@@ -5292,13 +4096,10 @@
         <v>191</v>
       </c>
     </row>
-    <row r="69" ht="12.8">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B69" t="s">
-        <v>573</v>
-      </c>
       <c r="C69" s="3" t="s">
         <v>193</v>
       </c>
@@ -5306,13 +4107,10 @@
         <v>194</v>
       </c>
     </row>
-    <row r="70" ht="12.8">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B70" t="s">
-        <v>574</v>
-      </c>
       <c r="C70" s="3" t="s">
         <v>196</v>
       </c>
@@ -5320,13 +4118,10 @@
         <v>197</v>
       </c>
     </row>
-    <row r="71" ht="32.8">
+    <row r="71" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B71" t="s">
-        <v>575</v>
-      </c>
       <c r="C71" s="3" t="s">
         <v>199</v>
       </c>
@@ -5334,13 +4129,10 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" ht="32.8">
+    <row r="72" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B72" t="s">
-        <v>576</v>
-      </c>
       <c r="C72" s="3" t="s">
         <v>202</v>
       </c>
@@ -5348,13 +4140,10 @@
         <v>203</v>
       </c>
     </row>
-    <row r="73" ht="12.8">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B73" t="s">
-        <v>577</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>205</v>
       </c>
@@ -5362,13 +4151,10 @@
         <v>206</v>
       </c>
     </row>
-    <row r="74" ht="12.8">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B74" t="s">
-        <v>578</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>208</v>
       </c>
@@ -5376,13 +4162,10 @@
         <v>209</v>
       </c>
     </row>
-    <row r="75" ht="12.8">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B75" t="s">
-        <v>579</v>
-      </c>
       <c r="C75" s="3" t="s">
         <v>211</v>
       </c>
@@ -5390,13 +4173,10 @@
         <v>212</v>
       </c>
     </row>
-    <row r="76" ht="12.8">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B76" t="s">
-        <v>580</v>
-      </c>
       <c r="C76" s="3" t="s">
         <v>214</v>
       </c>
@@ -5404,13 +4184,10 @@
         <v>215</v>
       </c>
     </row>
-    <row r="77" ht="12.8">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B77" t="s">
-        <v>581</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>217</v>
       </c>
@@ -5418,13 +4195,10 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" ht="12.8">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B78" t="s">
-        <v>582</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>220</v>
       </c>
@@ -5432,13 +4206,10 @@
         <v>221</v>
       </c>
     </row>
-    <row r="79" ht="22.35">
+    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B79" t="s">
-        <v>583</v>
-      </c>
       <c r="C79" s="3" t="s">
         <v>223</v>
       </c>
@@ -5446,13 +4217,10 @@
         <v>224</v>
       </c>
     </row>
-    <row r="80" ht="12.8">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B80" t="s">
-        <v>584</v>
-      </c>
       <c r="C80" s="3" t="s">
         <v>226</v>
       </c>
@@ -5460,13 +4228,10 @@
         <v>227</v>
       </c>
     </row>
-    <row r="81" ht="12.8">
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B81" t="s">
-        <v>585</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>229</v>
       </c>
@@ -5474,13 +4239,10 @@
         <v>230</v>
       </c>
     </row>
-    <row r="82" ht="12.8">
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B82" t="s">
-        <v>586</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>232</v>
       </c>
@@ -5488,13 +4250,10 @@
         <v>233</v>
       </c>
     </row>
-    <row r="83" ht="12.8">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B83" t="s">
-        <v>587</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>235</v>
       </c>
@@ -5502,13 +4261,10 @@
         <v>236</v>
       </c>
     </row>
-    <row r="84" ht="12.8">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B84" t="s">
-        <v>588</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>238</v>
       </c>
@@ -5516,13 +4272,10 @@
         <v>239</v>
       </c>
     </row>
-    <row r="85" ht="12.8">
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B85" t="s">
-        <v>589</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>241</v>
       </c>
@@ -5530,13 +4283,10 @@
         <v>242</v>
       </c>
     </row>
-    <row r="86" ht="12.8">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B86" t="s">
-        <v>590</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>244</v>
       </c>
@@ -5544,13 +4294,10 @@
         <v>245</v>
       </c>
     </row>
-    <row r="87" ht="12.8">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B87" t="s">
-        <v>591</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>247</v>
       </c>
@@ -5558,13 +4305,10 @@
         <v>248</v>
       </c>
     </row>
-    <row r="88" ht="12.8">
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B88" t="s">
-        <v>592</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>250</v>
       </c>
@@ -5572,11 +4316,66 @@
         <v>251</v>
       </c>
     </row>
+    <row r="89" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -5585,20 +4384,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="13.63" style="6" customWidth="1"/>
-    <col min="2" max="2" width="10.71" style="6" customWidth="1"/>
-    <col min="3" max="3" width="117.64" style="6" customWidth="1"/>
-    <col min="4" max="4" width="122.68" style="6" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="13.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="117.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="122.68"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5612,301 +4411,242 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="8"/>
     </row>
-    <row r="3" ht="12.8">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="8"/>
     </row>
-    <row r="4" ht="12.8">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="8"/>
     </row>
-    <row r="5" ht="74.6">
+    <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" t="s">
-        <v>593</v>
+        <v>267</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="6" ht="43.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B6" t="s">
-        <v>594</v>
+        <v>270</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="7" ht="43.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="B7" t="s">
-        <v>595</v>
+        <v>273</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8" ht="43.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="B8" t="s">
-        <v>596</v>
+        <v>276</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="9" ht="43.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="B9" t="s">
-        <v>597</v>
+        <v>279</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="10" ht="74.6">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="B10" t="s">
-        <v>598</v>
+        <v>282</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="11" ht="43.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B11" t="s">
-        <v>599</v>
+        <v>285</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="12" ht="43.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="B12" t="s">
-        <v>600</v>
+        <v>288</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" ht="95.5">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="B13" t="s">
-        <v>601</v>
+        <v>291</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="14" ht="32.8">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="B14" t="s">
-        <v>602</v>
+        <v>294</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="15" ht="32.8">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="B15" t="s">
-        <v>603</v>
+        <v>297</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="16" ht="12.8">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B16" t="s">
-        <v>604</v>
+        <v>300</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="17" ht="22.35">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="B17" t="s">
-        <v>605</v>
+        <v>303</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="18" ht="22.35">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B18" t="s">
-        <v>606</v>
+        <v>306</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="19" ht="200.7">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="200.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>607</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" ht="168.65">
+    <row r="20" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="B20" t="s">
-        <v>608</v>
+        <v>312</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="21" ht="241.75">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="B21" t="s">
-        <v>609</v>
+        <v>315</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="22" ht="32.8">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B22" t="s">
-        <v>610</v>
+        <v>318</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="23" ht="22.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="B23" t="s">
-        <v>611</v>
+        <v>321</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="24" ht="231.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B24" t="s">
-        <v>612</v>
+        <v>324</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -5914,20 +4654,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.7" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.61" style="1" customWidth="1"/>
-    <col min="3" max="3" width="109.15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="123.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="109.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="123.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5941,193 +4681,158 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="64.15">
+    <row r="5" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B5" t="s">
-        <v>613</v>
+        <v>327</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="6" ht="53.7">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B6" t="s">
-        <v>614</v>
+        <v>330</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="7" ht="22.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B7" t="s">
-        <v>615</v>
+        <v>333</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="8" ht="64.15">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B8" t="s">
-        <v>616</v>
+        <v>336</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="9" ht="64.15">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B9" t="s">
-        <v>617</v>
+        <v>339</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="10" ht="95.5">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B10" t="s">
-        <v>618</v>
+        <v>342</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="11" ht="64.15">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B11" t="s">
-        <v>619</v>
+        <v>345</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="12" ht="53.7">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B12" t="s">
-        <v>620</v>
+        <v>348</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="13" ht="74.6">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B13" t="s">
-        <v>621</v>
+        <v>351</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="14" ht="116.4">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>622</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="B14" s="5"/>
       <c r="C14" s="3" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="15" ht="147.75">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>623</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="16" ht="116.4">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>624</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="B16" s="5"/>
       <c r="C16" s="3" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="17" ht="168.65">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>625</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="B17" s="5"/>
       <c r="C17" s="3" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -6135,20 +4840,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.58" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.56" style="1" customWidth="1"/>
-    <col min="3" max="3" width="110.96" style="1" customWidth="1"/>
-    <col min="4" max="4" width="139.81" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="139.81"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6162,650 +4867,521 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3"/>
     </row>
-    <row r="3" ht="12.8">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3"/>
     </row>
-    <row r="4" ht="12.8">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3"/>
     </row>
-    <row r="5" ht="53.7">
+    <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B5" t="s">
-        <v>626</v>
+        <v>366</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="6" ht="126.85">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B6" t="s">
-        <v>627</v>
+        <v>369</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="7" ht="12.8">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B7" t="s">
-        <v>628</v>
+        <v>372</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="8" ht="126.85">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="B8" t="s">
-        <v>629</v>
+        <v>375</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="9" ht="105.95">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B9" t="s">
-        <v>630</v>
+        <v>378</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="10" ht="105.95">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="B10" t="s">
-        <v>631</v>
+        <v>381</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="11" ht="116.4">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B11" t="s">
-        <v>632</v>
+        <v>384</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="12" ht="43.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="B12" t="s">
-        <v>633</v>
+        <v>387</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="13" ht="32.8">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B13" t="s">
-        <v>634</v>
+        <v>390</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="14" ht="64.15">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B14" t="s">
-        <v>635</v>
+        <v>393</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="15" ht="22.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B15" t="s">
-        <v>636</v>
+        <v>396</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="16" ht="43.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B16" t="s">
-        <v>637</v>
+        <v>399</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="17" ht="32.8">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B17" t="s">
-        <v>638</v>
+        <v>402</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="18" ht="43.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B18" t="s">
-        <v>639</v>
+        <v>405</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="19" ht="53.7">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>640</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="20" ht="12.8">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="B20" t="s">
-        <v>641</v>
+        <v>411</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="21" ht="43.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B21" t="s">
-        <v>642</v>
+        <v>414</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="22" ht="32.8">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B22" t="s">
-        <v>643</v>
+        <v>417</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="23" ht="32.8">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B23" t="s">
-        <v>644</v>
+        <v>420</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="24" ht="32.8">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="B24" t="s">
-        <v>645</v>
+        <v>423</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="25" ht="44.75">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="B25" t="s">
-        <v>646</v>
+        <v>426</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="26" ht="32.8">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B26" t="s">
-        <v>647</v>
+        <v>429</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="27" ht="56.7">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="B27" t="s">
-        <v>648</v>
+        <v>432</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="28" ht="79.1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="B28" t="s">
-        <v>649</v>
+        <v>435</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="29" ht="44.75">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="B29" t="s">
-        <v>650</v>
+        <v>438</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="30" ht="13.8">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B30" t="s">
-        <v>651</v>
+        <v>441</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="31" ht="179.1">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B31" t="s">
-        <v>652</v>
+        <v>444</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="32" ht="12.8">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="B32" t="s">
-        <v>653</v>
+        <v>447</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="33" ht="13.8">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="B33" t="s">
-        <v>654</v>
+        <v>449</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="34" ht="91">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="B34" t="s">
-        <v>655</v>
+        <v>452</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="35" ht="12.8">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="B35" t="s">
-        <v>656</v>
+        <v>455</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="36" ht="105.95">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>657</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="B36" s="5"/>
       <c r="C36" s="3" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="37" ht="126.85">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>658</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="B37" s="5"/>
       <c r="C37" s="3" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="38" ht="126.85">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>659</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="B38" s="5"/>
       <c r="C38" s="3" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="39" ht="22.35">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>660</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="40" ht="74.6">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>661</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="B40" s="5"/>
       <c r="C40" s="3" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="41" ht="105.95">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="B41" t="s">
-        <v>662</v>
+        <v>473</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="42" ht="105.95">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="B42" t="s">
-        <v>663</v>
+        <v>476</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="43" ht="105.95">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="B43" t="s">
-        <v>664</v>
+        <v>479</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="44" ht="105.95">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="B44" t="s">
-        <v>665</v>
+        <v>482</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="45" ht="95.5">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="B45" t="s">
-        <v>666</v>
+        <v>485</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="46" ht="116.4">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="B46" t="s">
-        <v>667</v>
+        <v>488</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="47" ht="105.95">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="B47" t="s">
-        <v>668</v>
+        <v>491</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="48" ht="105.95">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="B48" t="s">
-        <v>669</v>
+        <v>494</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="49" ht="95.5">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="B49" t="s">
-        <v>670</v>
+        <v>497</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -6813,20 +5389,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.58" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.56" style="1" customWidth="1"/>
-    <col min="3" max="3" width="110.96" style="1" customWidth="1"/>
-    <col min="4" max="4" width="100.58" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="100.58"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6840,132 +5416,108 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3"/>
     </row>
-    <row r="3" ht="12.8">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3"/>
     </row>
-    <row r="4" ht="12.8">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3"/>
     </row>
-    <row r="5" ht="32.8">
+    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="B5" t="s">
-        <v>671</v>
+        <v>500</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="6" ht="168.65">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="B6" t="s">
-        <v>672</v>
+        <v>503</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="7" ht="220.85">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="B7" t="s">
-        <v>673</v>
+        <v>506</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="8" ht="231.3">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="B8" t="s">
-        <v>674</v>
+        <v>509</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="9" ht="210.4">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="B9" t="s">
-        <v>675</v>
+        <v>512</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="10" ht="314.9">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="B10" t="s">
-        <v>676</v>
+        <v>515</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="11" ht="112.65">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="B11" t="s">
-        <v>677</v>
+        <v>518</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="12" ht="199.95">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="B12" t="s">
-        <v>678</v>
+        <v>521</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/dialog.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/dialog.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="rumor" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="zone" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="unique" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="asmr" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="general" sheetId="1" r:id="rId3"/>
+    <sheet name="rumor" sheetId="2" r:id="rId4"/>
+    <sheet name="zone" sheetId="3" r:id="rId5"/>
+    <sheet name="unique" sheetId="4" r:id="rId6"/>
+    <sheet name="asmr" sheetId="5" r:id="rId7"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="679">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -791,87 +791,6 @@
   </si>
   <si>
     <t xml:space="preserve">I'm so happy, #pc! I'm truly happy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rob1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">見損なった{よ}！
-ひどい{よ}、やめて{くれ}！
-返り討ちにしてくれる{よ}。
-ごろつき風情に何ができるという{のだ}？
-やめて{くれ}。きっと後悔する{よ}。
-傭兵さんたち、このごろつきを追い払って{くれ}。
-ふん、この護衛の数が見えないの{か}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I misjudged you!
-Please, stop this!
-You'll regret coming after me.
-What makes you think a common thug can take me on?
-Please stop. You'll regret this.
-Mercenaries, drive this ruffian off.
-Hmph. Can't you see how many guards I have?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mama_yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ママだよ！
-{はい}、ママ{だ}～！
-ママはここにいる{のだ}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mommy's here!
-Yes, I'm your mommy!
-Mommy is right here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mama_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シッシッ！
-ママじゃない{よ}！
-君は何を言っている{のだ}？
-かわいそうに…頭を打ったの{か}？
-気持ち悪い{よ}…
-え…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoo, shoo!
-I'm not your mom!
-What are you talking about...?
-How pitiful... did you hit your head?
-That’s creepy...
-Huh...? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">baby_yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ママー！
-私の…ママなの{か}？
-マ…ママ…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mommy!
-...You are my...mommy?
-Ma... mama...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baby_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">こんなのママじゃない{よ}！
-君は何を言っている{のだ}？
-かわいそうに…頭を打ったの{か}？
-え…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You're not my mommy!
-What are you talking about...?
-How pitiful... did you hit your head?
-Huh...? </t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -1124,7 +1043,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">依頼が難しいと感じたら、名声を売ってしまうのも一つの手段{だ}。</t>
@@ -1970,7 +1889,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">ああ、いとも愛らしく安穏としたミシリアの都の一日だ。ミシリアの民は皆、目を塞いでいるかどこかに置き忘れてしまったのだろう。
@@ -2004,7 +1923,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Ah, what a lovely and peaceful day in Mysilia. All the people here must have closed their eyes or left them somewhere.
@@ -2061,7 +1980,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">I served in the royal court of Zanan long ago, but, well, I screwed up.
@@ -2090,7 +2009,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">私の家は、森の民の守護者の役職を代々受け継いできた。エレア達にとって苦難の時代の今、この称号が名ばかりでないことを証明したいよ。もちろん、そんな機会が訪れないのが一番だが。
@@ -2133,7 +2052,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Obviously the empire is a threat. but Zanan, who conceals her real intentions carefully, also creeps me out.
@@ -2962,6 +2881,1092 @@
 …Did I do a good job, Master…?
 …Milk? B-but…</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">这里有热腾腾的饭菜！用餐的话需要#1奥伦{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好了，请慢用{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在为受伤或生病而烦恼吗？支付#1的奥伦话，马上就可以开始治疗{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请不要乱动哦，马上就让{你}的身体恢复健康{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">背包中沉睡着未鉴定的物品？只要#1奥伦，就可以帮{你}全部鉴定{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{好}，请稍等一下，马上就开始鉴定{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好像没有需要鉴定的东西{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">需要#2块金块来扩展家园{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好，家园扩展完成{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">似乎无法扩展家园{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">现在，您向米西利亚支付的额外税金是#1{。}。想改变金额的话就告诉我{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{好}，您向米西利亚支付的额外税金变更为#1{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">现在您的账户里有#1奥伦的金币{。}。那么，您要存多少钱{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">现在您的账户里有#1奥伦的金币{。}。那么，您要取出多少钱{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{好}，确认您的钱已经存好了{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{好}，请取走您的钱{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好像没有用来会面的接待室{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看起来钱不够的样子{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{你}好像已经吃饱了{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{哇}，{你}愿意接受{我}的任务吗{。}？那就{拜托了}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{你}好像已经接了不少委托了呢。先去处理一下手头的委托吧{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">任务进展的顺利吗{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{哇}，委托顺利结束了吗！{谢谢}。这是约好的报酬{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{哇}，{我}也喜欢观鸟{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要上了{。}！
+呜嘿嘿。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这样啊{。}，那请先付{我}#1奥伦{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦，汝的伙伴已经相当成熟了啊？ 在长久旅途期间培育出的牵绊，现在正要迎来绽放的时刻。咱倒是能帮汝一把…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼呵呵呵呵呵呵，绽放吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼呵呵，那就要看汝的诚意了。来试着取悦咱吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">身材不错嘛{。}。{好}，{我}买了{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好啊，先给{我}#1奥伦吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么了{。}，#pc？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这好像是别人的遗失物{。}…算了，无所谓了{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{你}想让{我}成为{你}家的居民吗{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">很遗憾{。}，{我}还有其他事要做{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果{你}更有些魅力的话或许可以{。}。#newline(魅力需要#1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">给{我}把#1拿来吧{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{我}的兴趣是#1{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">喜欢的东西{。}？这个嘛，{我}对#1有兴趣{。}。顺便说一下，{我}最喜欢的东西是#2{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想买#2吗，客人您的品味不错啊{。}。价格是#1奥伦{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">从今天开始#1就是{你}的东西了{。}。请好好珍惜{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1吗？{好}，{我}给{你}带路{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{你}在开玩笑吗{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">将盟约之石升级到等级#2需要#1。#3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{好}，这样一来此地就能进一步发展了{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{你}对投资感兴趣吗？{你}到现在为止合计投资#2奥伦，#zone现在正在募集#1奥伦的投资{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{谢谢}！通过{你}的投资，#zone将来一定会发展得更好{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{你}要投资吗{。}？需要#1奥伦扩大这家店的规模{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{谢谢}！这样生意就能做的更好了{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{哇}{你}把#1送来了吗！{谢谢}。这就是约定好的报酬{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{哇}，这确实是#1。这就给{你}与这东西相称的报酬。{谢谢}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嚯，{你}有小奖章吗？收集小奖章就是{我}的人生意义啊！{我}这有很多引以为豪的作品，要和{我}交换吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{我}可不和罪犯做买卖。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{啊哈哈}，你这样的正经冒险者干嘛找我{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{你}想找谁？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#tg沉默了…)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#tg抱住了{你})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真是个无药可救的变态{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">终于恢复正常了吗{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#tg同意了)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#tg委婉地拒绝了)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特意给{我}送来了遗失物吗{。}。{你}真是市民的模范{。}。{谢谢}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这附近有个叫做#1的地方{。}。有兴趣的话不如去探索一番，也许会有不小的收获{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">很可惜{。}，最近没什么有用的消息{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是想要跟{我}试试吗{。}？
+{你}认真的{。}？
+{你}是想找{我}的麻烦{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{好}，胆子不小{。}！
+这就对了{。}！
+{好}，让{我}见识一下{你}的力量吧{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">什么{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{好}，今天开始我就是您的女仆{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{啊哈哈}，#brother，{你}很缺钱啊{。}？这样吧，用#1奥伦把{你}的名声卖给我{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{谢谢}，{我}会好好利用{你}的名声{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想要接受祝福{。}？{好}，把头低下来{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这把锁太复杂了{。}。不好意思{。}，你还是自己想办法吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你要帮我还钱吗…真是不好意思。那就先从小额的欠款账单开始处理吧。在纳税箱还过钱之后，就来向我报告吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这样啊…下一份账单也拜托你了。真是过意不去啊，等还清债务后，再来跟我聊聊吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欠款账单应该已经给你了。那是很重要的东西，可别弄丢了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这个嘛…我还没做好心理准备。不好意思，再稍微等等吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我不是告诉过你了吗？因为是重要的东西所以别弄丢了。 我再给你一张，这次要小心点啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的…我愿意。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好开心{。}。但必须要有婚礼许可证{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好开心{。}。但还是回到据点再慢慢聊吧{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真的吗？（现在的队伍将解散，组成和#tg两人的队伍）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好开心{。}，#pc！ 我真的很幸福{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好闲啊{。}。
+嗯？有什么事吗{。}？
+偶尔也想吃顿大餐啊{。}。
+永恒盟约…？{我}没听说过这个词{。}。
+想喝库莱姆酒，喝到醉醺醺{。}。
+猫为什么这么可爱呢{。}。
+#aka？…是谁啊{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{我}对经济有关的话题很感兴趣{。}。
+总之，在世上钱很重要啊{。}。
+有没有哪里掉了零钱啊{。}。
+白金币好难搞啊{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{我}喜欢讨论科学{。}。
+艾斯·泰尔是第七纪的文明{。}。该文明有着高度发达的科学{。}。
+艾斯·泰尔似乎认为魔法和科学是对立的{。}。
+据说在新王国耶鲁，机械人偶正在从事和人类一样的工作{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{我}喜欢去各种各样的地方旅行{。}。
+鲁米艾斯特作为艺术之城而闻名{。}。
+北提里斯有很多被称为奈菲亚的遗迹群，有很多遗迹和迷宫{。}。
+如果要去旅行的话，最好准备好充足的食物{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{我}对世界形势很感兴趣{。}。
+艾沃达纳是位于东大陆沙漠的强大帝国{。}。
+据说新王国耶鲁是由逃离帝国的奴隶们建立的{。}。
+总感觉泽纳恩被帝国的气息笼罩着{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信仰比什么都重要{。}。
+如果没有神的存在，这个世界就没有意义了{。}。
+据说治愈女神头上的翅膀的羽毛，拥有治愈任何疑难杂症的力量{。}。
+据说偶尔出现的大地摇晃是因为欧巴德斯在睡觉时翻身导致的{。}。
+库米罗妮大人是神还是女神这件事，让{我}在意到晚上睡不着觉{。}！
+幸运女神的真身其实是猫？{啊哈哈}，怎么可能有那样的事{。}！
+据传闻，机械之玛尼原本是人类{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在十年战争中，艾莱亚人对濒临危机的我们见死不救{。}。
+今后是人类的时代{。}！
+我们已经不需要艾莱亚人的帮助了{。}。
+艾莱亚人居住的森林，全部烧掉算了{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人类必须更加谦虚。应该向古老的种族充满敬意{。}。
+曾经，人类把艾莱亚称为母亲{。}。
+森林里的住民，似乎既不想干涉外界，也不希望被外界干涉{。}。
+为什么一定要去打扰森林住民的平静呢{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎光临。请慢慢看{。}。
+{我}这的货很全的{。}。
+经营一个店铺还是很难的{。}。
+如果不强大到能赶走流氓，就没资格当店主{。}。
+到其他商店卖东西可是会被压价的，{你}可要注意一下{。}。
+为了以防万一，{我}已经决定了店铺的继承人{。}。
+来，见识{我}引以为豪的商品吧{。}。
+最近不安分的家伙很多，很麻烦啊{。}。
+武器和防具如果没有好好鉴定，{我}就不能出高价收了{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保护市民的安全是守卫的工作{。}。
+看到可疑的人就向{我}报告{。}。
+{我}以前和{你}一样是个冒险者，直到…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">客人的钱比什么都重要{。}。
+有些东西靠钱可买不到{。}。
+欢迎光临本店{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊～啦，{你}真是个好#gender人{。}。让{我}送{你}一夜好梦吧{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这位客人也不是什么好人啊{。}。
+嘻嘻嘻…老板您真是个色鬼{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(感到无聊地看着{你})
+(#me瞥了{你}一眼，就转过身去)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">兔子的尾巴好像能呼唤幸运{。}。
+不要小看投石战士扔的石头{。}。
+在梦中能见到神吗{。}？
+好像有些在收集怪东西的贵族。{。}。
+在派对上演奏的时候，喝醉的客人偶尔会扔些奇怪的东西{。}。
+盗贼团的人好像经常使用什么奇怪的药{。}。
+旅行的魔法师用火焰的魔法给{我}烤肉了{。}。说实话，比店里的卖的都好吃{。}！
+挖不动岩石？试着用更硬的材料做镐子怎么样{。}？
+在这片大陆的某个地方，好像有居住着妖精的大树{。}。
+不交税的话会出大事的{。}。
+相信{我}！{我}看到了金色的雪波球{。}！
+据说有不可思议的灯能发出太阳光{。}。
+钓到大鱼就那样直接卖掉太可惜了{。}。
+知道吗？肚子饿了之后能吸收更多的营养{。}。
+如果想收集草药的话，可以去探索森林奈菲亚{。}。
+锻炼游泳就能增强耐力{。}！
+如果是美食家的话，好像能辨别蘑菇是否有毒{。}。
+锁住的宝箱，带到情报商那里就可以打开{。}。
+如果觉得委托很难的话，卖掉名声也是一种应对手段{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果{你}信仰库米罗妮，就可以从腐烂的食物中取出种子。
+不要把材质锤用在普通的装备上！
+高营养料理的真正功效会在喂宠物吃的时候发挥出来。
+在高质量的床上睡觉的话睡眠的效果会提高哦。
+对眩晕的敌人攻击能高概率打出会心一击。
+在毒、麻痹、出血等异常状态下，自愈将变得无效化。
+立方体在有异常状态时不会增殖。
+如果对古遗物使用重组卷轴，则可以让它重新生成。
+如果有足够的音抗性的话可以防止眩晕。
+有足够的幻惑抗性可以防止疯狂。
+祝福魔杖是个好主意，但据说效果比祝福的药水和卷轴稍差一些。
+湿的时候几乎不会受到火焰属性的伤害。但是受到电击属性的伤害会增加。
+短时间内吐太多会得厌食症。得了这种病只能喝东西充饥。
+被祝福的能力复苏药水和精神复苏药水，能够强化肉体和精神。
+可以向强敌投掷被诅咒的能力复苏药水和精神复苏药水。
+如果有游泳技能，就可以游到其他大陆去。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">听说有个很棒的戒指能增加{你}的手指。
+法杖放在地上一段时间就可以充能了！
+不知道该许什么愿？{你}可以试试许愿阿斯路的秘宝。
+宝石可以换成白金币。
+宝藏地图一定要祝福之后再读。
+喵…啊…啊啊…
+{你}的愿望是？
+在聊天窗口中喊出Guards！，守卫或许就会来帮忙哦。
+据说有一种方法可以让神成为宠物。
+在月门的前方等待着的是玩家杀手。
+{你}读了啊。读到这段文字的人*必定*会遭诅咒。
+{你}后面！小心！喂，快看，是妹—！快逃—！啊—！
+对{你}喵嘟噗喵嘟噗。
+由于您的存档文件损坏，无法正确显示幸运签。
+据说一猫不杀就会有好事发生。
+守卫好像很高兴被人裸体撞击。
+好像有妹妹专用的最强古遗物。
+在特尔斐附近建立牧场的话，马上就能成为有钱人了！
+如果善恶值高的话，可以让税金打折。
+怪物的粪便越重越能卖高价。
+喝被诅咒的恢复药水有时会生病。
+赫尔墨斯之血*一定要*祝福之后再喝！
+如果弄错了归还地点的话可能会很麻烦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果是办手续的话，请找秘书{。}。
+有什么事{。}？{我}很忙{。}。
+随时欢迎{你}投资城镇{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">来给城镇做些投资怎么样？
+{我}能帮上什么忙吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">露西亚|不归的船|当有人拿到这个瓶子的时候，我应该已经葬身海底了。不过天空真的很蓝。
+无名的士兵|最后的信|比剑更沉重的是恐惧。尽管如此我也希望有人知道，我没有逃跑。
+埃尔内斯|海潮的祈祷|神啊，如果没有平息波涛的力量，请至少给与我安眠。
+米蕾耶|约定的海滨|我先到的话就点燃篝火等你，可不要走错哦。
+领航员达罗斯|星的记录|今天星像也是正确的。出错的是我。
+塞雷娜|小小的告白|我只有一个遗憾，那就是没能唤出你的名字。
+老人|年轻时的日子|大海虽然会掠夺，但并不是一切都毫无意义。活下去。
+双胞胎妹妹|一半的世界|哥哥，世界还剩下一半呢。所以回来吧。
+船医雷纳特|医疗记录|我没能治好伤口，但让疼痛缓和了。这就足够了。
+伊莎贝尔|歌的后续|即使我不在了，也请把这首歌唱到最后。
+走私者凯尔|报酬的行踪|钱被沉入了北方的海湾。想要就去捞吧。
+见习神官罗亚|疑惑的告白|祈祷没有传达到。即使如此我也不会停止祈祷。
+渔夫哈尔德|最后的渔猎|今天没有渔获。但是和大海说了话。
+旅人希安|途经点|这里并不是终点。只是途经之处。
+王国书记官|官方记录摘抄|该船因风暴失事。报告结束。
+母亲|给孩子|记得天冷时要穿好外套。
+吟游诗人费伊|未完成的诗歌|韵律还是不行。致续写者。
+雇佣兵团长沃尔克|撤退命令|活着回去。名誉以后捡回来就行了。
+少女|第一次旅行|有点害怕。但是很开心。
+某人|给捡到的你|如果你读到了这个，证明世界还在延续。
+不明|我…|我要…回家…！
+不明|已经…|已经不行噗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在米西利亚，人类和艾莱亚生活的很和睦{。}。
+在十年战争中，这个国家承受了很大的损害{。}。
+乔南公的继承人埃夫隆德大人，基本没什么好传闻啊{。}。
+十年战争之后，这个国家被神秘的瘟疫袭击了{。}。有一种说法是，是尼米尔的奇迹之风，让疾病蔓延开来{。}。
+米西利亚今后会变成什么样呢{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎来到葡萄酒，温泉与樱花之村奥尔维纳。
+西奥露西亚真的对学习很热心，令人钦佩{。}。
+今年也满怀期待地等着湿衣大赛{。}！
+{我}想被法利斯狠狠地骂一顿{。}。
+奥尔维纳是米西利亚首屈一指的观光景点{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自从芙莉亚乌涅大人去世后，赛特拉斯大人就不怎么笑了{。}。
+虽然现在大家都把这个城堡叫做柳木堡{。}，但据说它以前有其他的名字{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎来到无法无天之人的城镇特尔斐。
+如果对那行当感兴趣的话，去盗贼公会就好了{。}。
+奴隶在这世上可是不可或缺的{。}。
+{我}就喜欢去竞技场见血{。}。
+这镇上没有守卫{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎来到帕罗米亚的王都。
+帕罗米亚什么都有，方便是方便{。}，但是实在太大了找人的时候会很辛苦{。}。
+贾比大人和斯塔莎大人的关系真的很好{。}。
+说起帕罗米亚名产，就是贵族的玩具{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这小村子的名字叫约恩{。}。
+如果需要马的话，在这里买就好了{。}。
+收获季总是人手不够{。}。
+村子算不上好，{你}随意慢慢逛吧{。}。
+听说西边有个犯罪者的城镇{。}。
+出了村子，沿着东边的路走就是王都帕罗米亚{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎来到水和艺术之城。
+听说有以温泉闻名的镇子{。}。
+在这城里，哪里都可以钓鱼{。}。
+绘画的话题烦死啦{。}。
+在帕罗米亚，只有这个城里有魔法师公会{。}。
+下水道味道很重，而且听说里面有可怕的怪物{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊嚏！嗯，今天也很冷{。}。
+每天都得铲雪真要命{。}。
+如果不能忍受罪恶感的话，去教会比较好{。}。
+好冷啊！
+{我}看到往南走一点的地方建了一个小工坊{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海风散发着清香{。}。
+{我}的兴趣是在宠物竞技场观看比赛{。}。
+如果想变得更强的话，去战士公会就好了{。}。
+这里的海产品在内陆地区卖得很好{。}。
+怎样才能进入金字塔呢{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们种了很多米，会卖给人类一些{。}。
+吉须阿弥大人是这个村子的守护神{。}。
+这个村子的河是从莱娜村附近的山上流出来的{。}。
+我们的祖先就是在这座山的山丘上开辟了梯田种起了稻子{。}。
+村里的人都懂书法{。}。
+如果{你}对书法感兴趣的话，可以在杂货店买到书法工具{。}。
+如果在田地旁边看到了金色的鬼火，请马上通知姬奴。那是会迷惑人的邪恶之灵{。}。
+这个村子里种着许多萝卜啊葱啊等等蔬菜{。}。
+姬奴真的很擅长培育大米{。}。
+只有信仰吉须阿弥大人的人，才能感受到这个村子的灵力{。}。
+前往莱娜村的旅人，都会在挑战山路前在这个村子的旅馆休息一下{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我害怕走出村子。因为人类会若无其事地摸我的耳朵和尾巴{。}。
+穗罗女大人守护着这个村子的大家{。}。
+我讨厌那些会破坏村子气氛的游客{。}。
+相传晚上一个人在樱花树旁边，就能看到金色的九尾狐{。}。
+这个村子的人从小就学习剑术{。}。
+这个村子里卖的奶是最棒的{。}！
+米芙会从南方进回稻子来在这里酿酒{。}。
+樱花酒是献给女神的最好供品{。}。
+美佐岐的身体真的很丰韵。又大又有包容力，最棒了{。}！
+多亏了美佐岐和美珠奈，这个村庄才能安全又繁荣{。}。
+这个村子在北地来说算是比较温暖的地方。神木在冬天也不会落叶{。}。
+樱花酒是这个村子的名产{。}。
+在瀑布下冥想可以让身体与心灵中的邪恶得到净化{。}。
+只有信仰穗罗女大人的人，才能看到这个村子真正的美丽{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">因为这里离城镇很远，所以几乎所有的物资都是从空中送来的{。}。
+斯普睿聚集着很多冒险者，他们会在挑战奈菲亚前互相组队{。}。
+斯普睿对于许多前往北提里斯荒野的冒险者来说，是最后的补给地点{。}。
+这附近有许多危险的奈菲亚{。}。
+据说这附近有着没有大使馆特别许可就无法探索的奈菲亚{。}。
+这个村子原本是妖精们居住的地方{。}。
+从冒险者们开始路经这里后，这个村子也变大了{。}。
+树上会不停地举行宴会，这就是我们从冒险者那里赚钱的方法{。}。
+斯普睿的创立者好像是穿着青色茄子服装的妖精{。}。
+多亏了妖精的魔法，这棵树不会因被人们居住而受到影响，仍能健康地成长着{。}。
+我们照顾树木，树木也保护我们{。}。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#race为什么来这个村子…？
+#race来这里做什么{。}？
+结界保护着这个村子，让这里不会受到怪物侵犯也不会被好奇的人盯上{。}。
+有时，我们需要从外面的世界获取研究材料{。}。
+对我来说很重要的人都早已去世，现在在外面的世界已经没有人记得我了{。}。
+我们打破了众神的禁忌，被施加了侍奉伟大之父的任务{。}。
+长老比切林似乎不太想提起自己已经活了多少岁月{。}。
+如果你能给我们带些尝起来不像灰的食物，大家都会很高兴的{。}。
+这个村子里几乎没什么食材{。}。
+我们不会迎来自然的死亡{。}。
+伟大之父认为我们的罪过都被偿付之时，就是我们被释放的日子{。}。
+我们所拥有的知识，如果传到外面的世界就太危险了{。}。
+伟大之父总是守护着我们。
+伟大之父监督着我们进行赎罪，这是无法逃脱的命运{。}。
+随着时间的流逝，我们已经没有什么物质层面上的追求了{。}。
+#race啊，在你面前的是活了一千年以上的流放者{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">……哔？
+…………哔哔
+哔………
+…哔波………
+……哔……错误……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这是什么地方？
+所谓的神，不过是比人类稍强，却又更加傲慢的家伙罢了。
+人类的行为，常常会因为感情的影响而出现执行错误。
+机械会损坏该怪设计得有问题吧？
+机械迟早有一天会取代人类统治这个世界吧。
+我记得我创造的一切事物。无一例外。
+…我怎会承认神这种不合理的东西。
+为什么这里有两个我？
+真是个无聊的地方。这地方有两个我的情况除外…
+…你说这只手臂？ 当然是我自己换的。
+你说我觊觎神的宝座…？ 哼，真是可笑。我都想拆开你的脑袋看看了。
+…这里的猫出奇的多啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好奇怪，什么都想不起来。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">塔内隆？ 噢，咱确实曾听到过有人这么称呼这个庭院。
+怎么，汝也想被咱宠爱么？ 
+时间在这里毫无意义。
+呵，汝是旅行至此，还是迷路至此？又或者是根本不知这里是哪里就随便闯了进来的笨蛋呢。
+呼呵呵，还特意向咱打招呼，真是有礼貌啊。
+这世间最棒的就是猫了。
+客人们迟早会忘记这个庭院，回到原本的时空。
+所有的灵魂，都可在这个庭院中得享安宁。
+被邀请到这个庭院的诸位，都怀着永恒安宁的碎片离开了。
+呼呵呵，汝也看得见吗？那些灵魂就像漂浮在水面上的花瓣一样，漂浮在时间无法触及的寂静中。
+庭院会记得所有曾在那寂静中入睡的灵魂。
+愿有朝一日能尽情抚摸幸运女神呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵，哥哥，你去哪里了？
+您好，旅行者。请好好享受在这里的时光吧。
+这里真是个和平的地方。待在这里仿佛都要忘记时间的存在了…
+我在去看戏剧的途中和哥哥走散了。到底发生了什么呢？
+其实哥哥和我都对戏剧没什么兴趣。只不过欣赏戏剧在泽纳恩来说可是一种身为贵族的修养呢。
+你知道吗…？ 亚尔蒂海特似乎有妖精哦？
+别看哥哥那样子，如果没有我的话他可是很邋遢的，呵呵。
+因为罗缇先生向演奏会场扔过石头，所以他被禁止入内了。
+我要是去给罗缇先生送些什么的话，他还是会像少年一样害羞呢。
+罗伊特尔…？ 不，我只认识罗缇先生…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哎呀，你听过那个变成野兽的王子的童话吗？
+我们是来自温戴尔之森的使者。
+为了谒见公正的贾比王，洗清森林和艾莱亚人民蒙受的不白之冤，我们正朝着王都帕罗米亚行进。
+艾索里亚大陆与提里斯大陆相隔一片汪洋，在提里斯北部的就是北提里斯。
+愿风加护于你。
+这里是哪里呢…？
+米西利亚？ 嗯，我知道。但米西利亚已经…
+我觉得人类…有点可怕。但也对他们很有兴趣。
+艾莱亚没有人类的大多数欲望。我们对占有、统治和争斗没有兴趣。至于这是不是好事，就另当别论了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看样子你好像不是北提里斯人呢。
+你在这个世界上会见识怎样的事情，又会留下怎样的足迹呢？
+看来我们迷路跑到了奇怪的地方啊。
+我们正在向帕罗米亚旅行的途中。
+你在说什么？ 现在是西埃尔历517年吧？
+开拓韦尔尼斯？ 你撞坏脑袋了吗？
+真巧呢。我照顾过和你很像的冒险者。
+真是麻烦，我们急迫的行程被昏倒的冒险者耽误了。
+…别摆出这么一副看到稀奇存在的表情呀。如你所见，我们是被你们称为「异形」森林的居民。
+踏出森林的艾莱亚不再会被森林接纳。当然，我和拉纳莱是特例。毕竟与人类打交道是「使者」的职责所在。
+拉纳莱是继承了特殊血统的艾莱亚。哎呀，让她听到就会被唠叨了，这个话题还是到此为止吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">少主作为帕罗米亚的继承人，希望他能更有操守一些。
+就因为有基尔巴德这样的人在，少主才会跟着瞎闹。
+斯塔莎公主在这个年纪举止就彬彬有礼，而且行事果断。简直就是宫廷的偶像！
+斯塔莎公主万岁！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我和米拉尔在小到拿不动锤子的时候就是孽缘搭档了。
+就连我也非常认可米拉尔的才能。但这个家伙居然放着客户的订单不管，一直做什么猫玩具，真是可悲啊。
+无聊啊。难道就没有让我那蒙灰待燃的工匠之心再能燃烧起来的大委托吗！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼哈哈哈！…你是什么人？
+以欧巴德斯之名，接近斯塔莎公主的臭虫我会全部消灭的，呼哈哈哈！
+公主万岁！
+我也想在15年前的战争中展现风采啊！
+呼哈哈！
+帮助弱者，粉碎邪恶！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">来米西利亚宫廷有什么事吗？
+我也老了。但现在还不是隐退的时候。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冒险者在这里做什么？
+孤儿院会养护并教育没有父母的孩子。
+即使在这世道下，我也希望孩子们能健康地成长。
+教育很重要。这些没有任何后盾的孩子，总有一天也要找份糊口的工作才行。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的名字是斯兰。是为帕罗米亚效力之人。现在为了修行而在各地旅行。
+话说回来贵重的书籍很多呢。
+在暴风雪的日子里到达了这座孤城，这阵子要承蒙照顾了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦哦，是客人啊！来来，不用客气，和我的猫儿们尽情嬉戏吧。
+我和搭档在工房的商号问题上吵架了。如果他有一点品味的话，就不会想出「盖罗克米拉尔」这种怪名字了吧。
+今天吃什么好呢。最近琢磨猫的食谱比当铁匠还开心。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">行商的生活很无忧无虑，但是待在住得很舒服的镇上也不错。说起来，卡普尔附近就不错。
+兽人商人很少见吗？在提里斯可能很难看到吧。
+我收集的商品西到海洋之国维利察，东至沙漠黄金乡尼萨。请慢慢看。
+不…这可不是头饰。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我是代理市长诺拉。有什么事吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哎呀，您找我有什么事吗？
+帕罗米亚是历史悠久的提里斯大国。我很荣幸被这个王宫接纳。
+偶像…？…是异国语言吗？
+在王宫的粉丝……啊……大……大家对我都很好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我对历史和传承很感兴趣。
+法利斯姐姐一生气就很可怕。
+帕罗米亚的王宫图书馆里有很多藏书，真是好地方。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你是冒险家吗？一定要给我讲讲你的各种故事。
+父亲太严厉了。什么事都要挨个唠叨，真麻烦。希望科内利安不会受到不好的影响…
+基尔巴德和科内利安是从小就是朋友。即使有主从关系，但他们的友谊不会改变。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你谁啊？
+这里不是冒险者之流该来的好地方。快给我离开。
+……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你是什么东西？不要随便和我搭话。
+啊，真了不起，米西利亚之都又迎来安稳祥和的新一天了。米西利亚人民莫不是都瞎了眼，还是把眼珠子都丢了呢。
+一个个的脸上都摆着悠闲的表情呢，一群蠢货。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请不要太靠近…埃夫隆德大人会生气的。
+异形之森？…我没有去过。住在米西利亚的艾莱亚都是「森林外」的艾莱亚。
+像这样看着花很容易犯困呢…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要听首歌吗？
+我以前侍奉着泽纳恩的王室，但是，我搞砸了…
+现在米西利亚才是我的故乡。
+看见梅尔文那家伙了吗？我刚好想唱一首歌呢。
+我的妻子是米西利亚最美丽最聪明的人。我简直配不上她。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妹妹嫁到贝里希身边已经八年啦。时间过得真快。
+我家世世代代继承了森之民守护者的职务。在这个苦难时代，我想证明这个称号不仅仅是名字而已。当然，没有证明的机会才是最好的。
+我的搭档格里芬是野生的猫头鹰。当时它受了伤，是我给它治好了。后来被它缠上，现在它好像觉得我的肩膀就是它的栖木。
+妇女们缺乏节操真叫人为难。
+埃夫隆德大人身边的有个叫艾露米纳雷的女孩，那个女孩难道……不，也许我想多了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你是什么人？
+虽然冒险者这名字听起来不错，但他们不就是一群不愿工作的流浪汉吗？
+帝国的威胁自不必说，一直小心隐藏着真实意图的泽纳恩也让人毛骨悚然呢。
+据说帕罗米亚的泽茵王是有名的君主，而他的儿子贾比王子则是个玩世不恭的公子哥。看来任何国家都会为继承人的问题烦恼啊！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妹和立方体，哪个可怕？虽然我觉得妹更可爱一些。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你好啊，渡鸦。有什么事吗。
+来喝杯茶吧，渡鸦。
+我是『探求者』…也被称为『异界来客』。如你所见，我是个隐士。我为了获取世界上所有的知识献出了一切。
+…不过，亏你能找到这么偏僻的地方来啊。
+…这座城是属于我的大图书馆，不过图书馆好像就该敞开大门迎接众人来访…所以我欢迎你的到来。
+任何人都有获取这世界上所有的知识的权力。你在此处自由行动即可。
+在这个世界的某个地方，好像有刻着伊尔瓦全部历史与真相的秘宝…。
+永恒盟约…？这么古老的故事你也知道啊。
+你好，渡鸦。借你的书有认真读吗？
+把知识留给后世是获得知识之人的义务。
+你好，渡鸦。你有见过我的朋友斯兰吗？
+…这个头盔？它是很美的野兽吧。它是我的老朋友。
+……遮住脸的理由？10年战争之后，艾莱亚一直抬不起头啊…。
+……朋友们都先一步踏上旅途…。
+好像有个追逐妹犬之馆幻觉的疯子。
+战争还会发生吗。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你能听到风在用古老的语言低语吗？我为了学习风的故事，正在游历世界。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我讨厌那些小鬼。他们一直在说些奇怪的话，真是讨厌！
+别拿我和那些怪物混为一谈。
+爸爸回来之后，我要让爸爸再也不带我来这里！
+我爸爸是｢科学家｣。来到这个托儿所后…那个怪物女就拜托爸爸帮她做什么事，爸爸还说很快就能回来…
+爸爸很快就能回来的。
+就算求我，我也不会和那些小鬼玩的。
+那些小鬼真是的，有时候还会捡回来一些奇怪的东西呢。
+那个怪物女才不是我妈妈呢。谁看了也知道不是才对吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哎呀，你是来玩彩球抽奖的吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们既是祝福，也是诅咒。换个角度看，弱小也是一种强大。
+没有死亡的生命，没有地狱的天堂，没有离别的相遇，没有悲伤的喜悦…这样的世界是不存在的。
+我作为福缘之圣女，肩负着每年引导村庄举行封印仪式的职责。
+吉须阿弥大人的祝福普济众生。那份力量是足以干涉世界，没有信仰的人也能够感受到。
+我们培育的稻子寄宿着丰富的灵力，是封印仪式上不可或缺之物。
+喻部是一个扭曲的负之神，他想要消除众神之间所有的争斗，试图把理想和平带给伊尔瓦。
+决定继承圣女身份的时候，我舍弃了以前的名字，自称「姬奴」。总有一天，我的某个女儿也会踏上同样的道路。
+夏无永驻，四季轮回，寒冬将至。祝福也不会永远持续，不幸亦然。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">喻部是一个邪恶的负之神，他操纵着众神的战争，企图统治伊尔瓦。
+我们会在神树广场上献上仪式之舞。
+穗罗女大人爱着所有的生命，甚至会给予那些没有信仰的人小小的祝福。
+作为金剑之圣女，我每年都要为封印仪式献上剑舞。
+樱花的花瓣像女神的眼泪一样飘落，在我们的心中刻下转瞬即逝的美。
+仪式用的刀剑在祭拜女神时起着重要的作用。
+穗罗女大人对孩子们都很慈爱，她会为大家族祝福。涅芙一族算不上什么成员众多的种族，其中的大家族都很受尊敬。
+我的刀是历代圣女代代相传的。
+金剑之圣女们都立志用此刀创造新的传说。
+女神教导我们力量和美并非是对立的。涅芙的剑舞便是这两者的结合。
+涅芙的村庄是为了保护神树而建造的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你是冒险者吗？竟然来到这样的地方，真是好奇心太旺盛了。
+我主要负责守护这里。虽然很光荣...但有时候好无聊啊。
+耶万大人的教导会被认为是残酷的，但那也是源自于对凡人的厚爱与期待。
+我讨厌机器。因为它们不会流血。
+来试试身手怎么样？最近的争斗完全不够。
+比利先生如果没有那些刺的话...
+猫真是可爱的生物...
+我留恋于战场上的硝烟。可以带我去吗？
+这里的景色很美，但是生活很不方便。只有去北方的米芙村玩才算得上是偶尔的乐趣。
+如果你想挑战沉睡在这里的负之神，我是不会阻止的。我想耶万大人也会很高兴才是。
+以太是一种非常有趣的物质。无论好坏，都会左右今后人类的前途。
+不觉得摸初次见面的狐族很失礼吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这条项链？里面装的当然是米啦。因为我们村里没有种小麦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这家旅馆原本是为了迎接朝圣者而建造的，但是最近接待的游客也变多了。
+欢迎光临！要吃饭吗？还是洗澡？还是…？
+不知道为什么村子会突然变得很热闹，不过，忙起来的感觉也不坏！
+游客们总是不顾美佐岐的警告，太过靠近圣树，真让人头疼。真是的，一点敬畏之心都没有。
+我们虽然可以自给自足，但是如果不从米芙村运来食物的话，根本招待不了这么多游客。
+为什么人类对我们的耳朵和尾巴那么感兴趣呢？
+美佐岐负责守护神殿，我负责管理旅馆。这样看来好像没什么长老能做的事了呢！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你想知道我为何被制造出来吗？不想？猜你也不想。
+我梦到一个像家一样的地方，但我想不起来该如何回到那里。
+我醒来时就拿着这个武器。它可真重啊。这是拿来刺的？还是用来射击？应该都行吧。
+「你好！我是大家的偶像，机械人偶机利亚～！」…我还装有偶像模块吗？这是什么时候录的？
+据说机械之玛尼会向聆听虚无之人低语。如果是那个人的话，可能会知道我为什么被制造出来。
+*zzt* 记忆又故障了…我来这里要干什么来着？
+*beep* 现在正在进行定期维护。请再稍等一下。
+你说我是小号的魔像？怎么可能呢。
+错误？故障？才没有，那只是我的功能罢了。
+*盯着看*啧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天蓝色的郁金香？我虽然去过很多地方，但是从没见过那种东西哦。
+最近好像有什么奇怪的新病在流行着……不知会不会长出角来呢～。
+如果惹恼了某些神明就可能会被降下古怪的诅咒，要小心哦。
+赌场的庄家绝对在｢出老千｣……！ 
+蛋的蛋♪刺身的刺身♪刺身的蛋♪
+人外有人，杂鱼外有杂鱼。#brother2是哪边呢？
+我本来还有另一根角……不对是刀，但在旅途中丢失了。
+享用美食的时刻最幸福♪
+牙姬酱驾到。快来招待一下啦。
+牙姬酱就是可爱又强大☆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你我的灵魂能够再次交织，不正意味着到了我们实现约定的时候吗…？ 
+若你就是我所寻求之人…那命运一定会轻轻向我们诉说吧。
+我能在你身上感受到一种好像已经在漫长时空中丢失的安宁感。
+你的灵魂让我感到如此熟悉…就仿佛在言语诞生之前，你我就已曾邂逅。
+若此刻能够永远持续下去就好了…我还想再多感受一下你的温暖。
+你只是一位温柔的陌生人吗…又或者真的是我跨越时空追寻的那道身影呢…
+我还是没法叫出现在就在我面前的…你的名字…
+真是不可思议…只要待在你身边，就会感觉十分安心。
+你也感觉到了吗…？那条连接着你我之间的命运之线？
+无论走过多少路…旅途的前方都一定会有你在。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你在意我是什么时候出生的吗#brother2？那是很久很久以前的故事了#brother2…
+我一直为了寻找#brother2而在这个世界上徘徊…然后就找到了#brother2！
+#brother2会和我永远……在一起吧…？我只是有点不安而已啦#brother2。
+为了#brother2，无论战斗还是家务，都要做好才行。
+神有时很残酷呢#brother2…
+我没有束缚#brother2哦！真的哦！
+我的歌声中似乎寄宿着混沌的力量。
+除了我以外这个世界上还有着许多和#brother2没有血缘关系的妹妹！
+好想摸雪波球！也想摸#brother2！
+雪波球有不同颜色的哦#brother2。如果能都带回家就好了#brother2。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我叫娜娜苏，是茄子妖精哦～。
+你问我喜欢的东西是什么？当然是茄子啦～。
+斯普睿是个非常好的地方哦~大家都在开心地跳舞呢～。
+冒险中得到宝物当然很开心，但最开心的是一起冒险得到的羁绊哦～。
+我经常和冒险途中遇到的新朋友一起喝酒。非常开心呢～。
+当然也发生过悲伤的事情，但我仍然相信今后还会有新的邂逅所以在不断前进，这就是现在的我～。
+虽然相遇总有一天会结束，但我觉得在那之中得到的东西绝对不是徒劳哦～。
+据说是一只青色茄子的妖精创建了斯普睿……希望我有朝一日能试着超越她呢～。
+其实我小时候曾和青色茄子的妖精对练过哦。她虽然是妖精，但是很强壮呢～。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我是莱伊娜！随便碰我的话会被电麻的！
+哎呀，冒险者。找我有什么事？
+和珀伊娜的关系？嗯～只是恶作剧伙伴而已？不过我们搭档冒险已经很久了。
+我并不讨厌娜娜苏哦？只是…想稍微捉弄一下，把她变成烤茄子！呀哈哈！
+我和珀伊娜、娜娜苏三个人第一次一起去冒险的时候，差点因为娜娜苏冒失死掉…多亏我机智才有了转机。真是的…
+虽然争夺包的时候我和娜娜苏是对手，但我偶尔也会和娜娜苏一起冒险哦。不过她基本都是负责去当诱饵啦！呀哈哈！
+包括我在内，最近斯普睿愿意去冒险的妖精变多了。不过竞争对手增加也不是什么坏事啦！
+…我发烧的时候，娜娜苏照顾过我。那时候的我无法好好向她道谢，但是我真的很感激。
+你问创立斯普睿的青色茄子妖精…？啊，她啊…以前我曾和她对练过，但是从没赢过！
+我本来还想着要从青色茄子妖精那扳回一局呢，但是不知什么时候她就离开了！…赢了就跑，真气人！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我是珀伊娜，你要是敢多说废话就毒死你。
+…怎么？有什么事么？
+莱伊娜有时候把战斗想得太简单。说了多少遍冒险不是玩游戏，真是个笨蛋…
+娜娜苏太天真了。她说她很重视羁绊，但总有一天她会被那羁绊绊倒的…
+我和莱伊娜也算认识很久了，我只把她当成是恶作剧的伙伴。不过我并不讨厌和她一起冒险。
+我更喜欢发动奇袭，但是莱伊娜总是会立刻冲锋陷阵造成无谓的消耗…太笨了…
+你听莱伊娜说过和娜娜苏第一次冒险的事吗？那时候娜娜苏让大家遭遇了危险，后来还哭了鼻子，哈哈。
+…以前有次我丢了东西，娜娜苏还拼命的帮我找。明明平时我总是对她搞恶作剧之类的…真是个笨蛋…
+我和娜娜苏还有莱伊娜曾经一起受过青色茄子的妖精的训练。但是我的毒攻击对她几乎没有效果。
+也不知现在的我加上莱伊娜还有娜娜苏能不能联手打赢青色茄子的妖精。只是她从很久以前就不知去向了…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪波球酱，真可爱啊……嘿嘿嘿……。
+真羡慕自由自在的猫咪。如果世上有猫咪的神明，那一定是自由的化身吧。
+明明只想平凡度日，为什么麻烦总是找上门呢……*叹气*
+我也不知道自己是怎么和那位说话方式奇奇怪怪的冒险者完成交流的……。
+那个可爱的人偶冒险者，一直在寻找着谁呢……。
+那位黑翼的冒险者，好帅啊……。
+那位法师冒险者，好像带着本危险的书呢……。
+那位相信命运引导的冒险者，总感觉很热情呢。
+听说有位吸……猫？的冒险者……？
+米西利亚的魔女面包师，真是太厉害了！既是魔女，又是面包师！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的料理中使用的都是顶级食材。
+想不想看看我的扫把收藏？
+嗯嗯…蝾螈的舌头…蜜蜂的眼睛。啊嗯？ 抱歉，没注意到你在这里。我正在思考新的食谱呢。
+咦，你有看到这附近有只猫吗？
+面包当然要用窑做呀？
+药品柜？  你给我好好看看，这是香料柜！
+我的帽子？　呵呵，很漂亮吧？
+（魔女把装满一袋的虫子哗啦一声都倒进了搅拌盆里。）
+……你的问题真多啊…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…哔—…
+…沙沙沙…
+…沙沙…嘎嘎…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…抚摸…抚摸…
+…抱抱…
+…紧抱…
+…乖…乖…
+…笨…笨蛋…
+…别…别误会了…
+…才…才不是…为了你呢…
+…才…才不是…
+…只…只是想打发无聊的时间罢了…
+…嗯…嘿咻…
+…被治愈吧…
+…呼…
+…咳…咳…
+…迷茫的…人们啊…
+…治…治愈…
+…受伤的…灵魂…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…嘎吱…嘎吱嘎吱…
+…轰轰轰轰……
+…咯吱咯吱……
+…垮拉……
+…轰隆…哗啦……
+…咔哩…咔哩咔哩……
+…轰……轰—……
+…咯吱…咯吱吱吱……
+…咔吧……嘎吧吧……
+…喳啦……喳啦喳啦……
+…咚……咚……
+…咣……咣……
+…咚……
+…呼哈哈哈哈哈哈哈……
+…呼哈哈……呼哈啊……
+…呼哈—……
+…呼……呼哈……
+@3呼哈哈哈哈哈哈哈！ 
+@3呼哈—
+…呼呼……
+…呼—…！ …呼—…！……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…别怕…妈妈会一直在你身边…
+…晚安…好孩子…
+…可以来…妈妈怀里哦…
+…只是好好活着…就很了不起了…
+…来…让我摸摸头…放心吧…
+…来…放松下来…
+…乖乖…
+…就这样…暖暖和和地…
+…摸摸…摸摸…力气，放松…
+…嗯…乖乖…好孩子…
+…就这样…暖暖的…
+…什么都…不用想了…
+…毛茸茸的…很安心吧…
+…用这尾巴…把你卷起来…
+…松松…软软…来…尾巴…
+…轻轻地…轻轻地…温柔…卷起…
+…温暖…温暖…你困了…
+…就这样…紧贴在一起…
+…吸…哈啊…一起…呼吸…
+…妈妈在哦…
+…摸摸…摸摸…力气，放松…
+…来…*紧紧抱住*…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…呵呵呵……
+…呵呵……
+…呵……呵呵呵……
+…呵呵……呵呵…
+…回去吧……
+…回到元素之中……
+…回归……
+…向元素之中……呵呵……
+…呵……呵……呵……
+…呵……呵……
+…呵呵……呵……
+…快……
+…呵呵呵呵……
+…呵呵呵呵呵……
+…呵呵……呵呵……呵呵……
+………
+………
+……猕猴桃……呵呵……
+……
+… </t>
+  </si>
+  <si>
+    <t xml:space="preserve">…哼…你喜欢这种的…？
+…真是个变态…
+…你这…蠢猪……啊哈哈……！
+…哎呀…在发抖呢……真可怜…
+…你喜欢…被看不起的感觉吧…？
+…区区蝼蚁……啊哈哈哈…
+…好小……真的……好小……
+…啊哈……真可笑……
+…啊哈哈……杂碎……真是杂碎……！
+…真可悲……
+…来…露出更多丑态吧…
+…在女神面前…真亏你能做出那种表情…
+…啊哈哈…可悲的猪猡…
+…那表情…真是…丢人至极…
+…快…给我趴在地上吧…
+…啊哈…连风都在嘲笑你…
+…谁允许你…直视女神了……？
+…再敢抬头的话…就把你剁成肉酱…
+…啊哈…可悲的凡人啊…
+…真是…好懂呢…
+…啊哈哈…没救的家伙…
+…丢人的家伙…挨了骂…还乐在其中…
+…这个…变态…
+…啊啊…刚才的…很让你开心吧…？
+…垃圾…
+…你就这样…毫无价值地存在下去吧…
+…你…该不会另有所图吧…？
+…啊啊…猜中了……啊哈哈！
+…光是存在就让人觉得…不舒服呢…啊哈…
+…真的是…无药可救的变态啊……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@3喵咪咪！
+@3帝王蟹！
+…蹭…
+…蹭蹭…
+…舔…
+…舔舔…
+…咚…
+…喵咪…
+…咪咪咪…
+…咪…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…早上好，主人…
+…这就为您奉上茶水…
+…您不在的时候，宅邸的事务我都管理好了…
+…家族中只有我的胸部这么小…不甘心…
+…梯子…放到哪里去了…？
+…啊…您脸上沾上东西了哦…
+…请让我代替主人…来处理吧…
+…我还要捣…多久年糕呢…？
+…呀啊！…
+…主、主人…！
+…照顾您是女仆的职责……但就算不是职责，我也会做的…
+…今天的晚餐…想吃点什么呢，主人…？
+…来，张…嘴…♥
+…我听说甲鱼…十分的滋补…
+…架子高处的东西，不用抱起我也可以拿得到哦…？
+…和主人靠得这么近…作为女仆，有点静不下心…
+…记得适当运动哦…？
+…我…做的好吗，主人…？
+…奶…奶吗…？ 但、但是……</t>
+  </si>
 </sst>
 </file>
 
@@ -2981,19 +3986,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -3007,7 +4012,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -3020,7 +4025,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -3046,7 +4051,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -3055,82 +4060,82 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3205,7 +4210,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3215,11 +4220,11 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
+      <xdr:colOff>275760</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>113040</xdr:rowOff>
+      <xdr:rowOff>114480</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="0" name="Rectangle 2" hidden="1"/>
         <xdr:cNvSpPr/>
@@ -3227,13 +4232,13 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49653720" cy="113040"/>
+          <a:ext cx="49655160" cy="114480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="ffffff"/>
+          <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
         <a:ln w="9360">
           <a:solidFill>
@@ -3361,20 +4366,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
-  <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D88"/>
+  <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="95.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="86.34"/>
+    <col min="1" max="1" width="19.11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.41" style="1" customWidth="1"/>
+    <col min="3" max="3" width="95.53" style="1" customWidth="1"/>
+    <col min="4" max="4" width="86.34" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3388,13 +4393,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="12" customHeight="1"/>
+    <row r="3" ht="12" customHeight="1"/>
+    <row r="4" ht="12" customHeight="1"/>
+    <row r="5" ht="12" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>510</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
@@ -3402,10 +4410,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="20.1" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>511</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
@@ -3413,10 +4424,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="20.1" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B7" t="s">
+        <v>512</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
@@ -3424,10 +4438,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="20.1" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="B8" t="s">
+        <v>513</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
@@ -3435,10 +4452,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="20.1" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
@@ -3446,10 +4466,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="20.1" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="B10" t="s">
+        <v>515</v>
+      </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
@@ -3457,10 +4480,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="20.1" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="B11" t="s">
+        <v>516</v>
+      </c>
       <c r="C11" s="1" t="s">
         <v>23</v>
       </c>
@@ -3468,10 +4494,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="20.1" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="B12" t="s">
+        <v>517</v>
+      </c>
       <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
@@ -3479,10 +4508,13 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="20.1" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="B13" t="s">
+        <v>518</v>
+      </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
@@ -3490,10 +4522,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="20.1" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="B14" t="s">
+        <v>519</v>
+      </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
@@ -3501,11 +4536,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="20.1" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="C15" s="3" t="s">
         <v>35</v>
       </c>
@@ -3513,10 +4550,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="20.1" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="B16" t="s">
+        <v>521</v>
+      </c>
       <c r="C16" s="1" t="s">
         <v>38</v>
       </c>
@@ -3524,10 +4564,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="20.1" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="B17" t="s">
+        <v>522</v>
+      </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
@@ -3535,10 +4578,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="20.1" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="B18" t="s">
+        <v>523</v>
+      </c>
       <c r="C18" s="1" t="s">
         <v>44</v>
       </c>
@@ -3546,10 +4592,13 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="20.1" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="B19" t="s">
+        <v>524</v>
+      </c>
       <c r="C19" s="1" t="s">
         <v>47</v>
       </c>
@@ -3557,10 +4606,13 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="20.1" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="B20" t="s">
+        <v>525</v>
+      </c>
       <c r="C20" s="1" t="s">
         <v>50</v>
       </c>
@@ -3568,10 +4620,13 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="20.1" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B21" t="s">
+        <v>526</v>
+      </c>
       <c r="C21" s="1" t="s">
         <v>53</v>
       </c>
@@ -3579,10 +4634,13 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="20.1" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="B22" t="s">
+        <v>527</v>
+      </c>
       <c r="C22" s="1" t="s">
         <v>56</v>
       </c>
@@ -3590,10 +4648,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="20.1" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="B23" t="s">
+        <v>528</v>
+      </c>
       <c r="C23" s="1" t="s">
         <v>59</v>
       </c>
@@ -3601,10 +4662,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="20.1" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
+      <c r="B24" t="s">
+        <v>529</v>
+      </c>
       <c r="C24" s="1" t="s">
         <v>62</v>
       </c>
@@ -3612,10 +4676,13 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="20.1" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="B25" t="s">
+        <v>530</v>
+      </c>
       <c r="C25" s="1" t="s">
         <v>65</v>
       </c>
@@ -3623,10 +4690,13 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="20.1" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="B26" t="s">
+        <v>531</v>
+      </c>
       <c r="C26" s="1" t="s">
         <v>68</v>
       </c>
@@ -3634,10 +4704,13 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="20.1" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="B27" t="s">
+        <v>532</v>
+      </c>
       <c r="C27" s="1" t="s">
         <v>71</v>
       </c>
@@ -3645,10 +4718,13 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="20.1" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="B28" t="s">
+        <v>533</v>
+      </c>
       <c r="C28" s="1" t="s">
         <v>74</v>
       </c>
@@ -3656,10 +4732,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="20.1" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>76</v>
       </c>
+      <c r="B29" t="s">
+        <v>534</v>
+      </c>
       <c r="C29" s="3" t="s">
         <v>77</v>
       </c>
@@ -3667,10 +4746,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="20.1" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="B30" t="s">
+        <v>535</v>
+      </c>
       <c r="C30" s="1" t="s">
         <v>80</v>
       </c>
@@ -3678,10 +4760,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" ht="20.1" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="B31" t="s">
+        <v>536</v>
+      </c>
       <c r="C31" s="5" t="s">
         <v>83</v>
       </c>
@@ -3689,10 +4774,13 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" ht="20.1" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="B32" t="s">
+        <v>537</v>
+      </c>
       <c r="C32" s="1" t="s">
         <v>86</v>
       </c>
@@ -3700,10 +4788,13 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" ht="20.1" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
+      <c r="B33" t="s">
+        <v>538</v>
+      </c>
       <c r="C33" s="5" t="s">
         <v>89</v>
       </c>
@@ -3711,10 +4802,13 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="A34" s="1" t="s">
         <v>91</v>
       </c>
+      <c r="B34" t="s">
+        <v>539</v>
+      </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
@@ -3722,10 +4816,13 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="22.35">
       <c r="A35" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="B35" t="s">
+        <v>534</v>
+      </c>
       <c r="C35" s="3" t="s">
         <v>77</v>
       </c>
@@ -3733,10 +4830,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="B36" t="s">
+        <v>540</v>
+      </c>
       <c r="C36" s="1" t="s">
         <v>80</v>
       </c>
@@ -3744,10 +4844,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="A37" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="B37" t="s">
+        <v>541</v>
+      </c>
       <c r="C37" s="1" t="s">
         <v>97</v>
       </c>
@@ -3755,10 +4858,13 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="A38" s="1" t="s">
         <v>99</v>
       </c>
+      <c r="B38" t="s">
+        <v>542</v>
+      </c>
       <c r="C38" s="1" t="s">
         <v>100</v>
       </c>
@@ -3766,10 +4872,13 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.8">
       <c r="A39" s="1" t="s">
         <v>102</v>
       </c>
+      <c r="B39" t="s">
+        <v>543</v>
+      </c>
       <c r="C39" s="1" t="s">
         <v>103</v>
       </c>
@@ -3777,10 +4886,13 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.8">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="B40" t="s">
+        <v>544</v>
+      </c>
       <c r="C40" s="1" t="s">
         <v>106</v>
       </c>
@@ -3788,10 +4900,13 @@
         <v>107</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="12.8">
       <c r="A41" s="1" t="s">
         <v>108</v>
       </c>
+      <c r="B41" t="s">
+        <v>545</v>
+      </c>
       <c r="C41" s="1" t="s">
         <v>109</v>
       </c>
@@ -3799,10 +4914,13 @@
         <v>110</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" ht="12.8">
       <c r="A42" s="1" t="s">
         <v>111</v>
       </c>
+      <c r="B42" t="s">
+        <v>546</v>
+      </c>
       <c r="C42" s="1" t="s">
         <v>112</v>
       </c>
@@ -3810,10 +4928,13 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="12.8">
       <c r="A43" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="B43" t="s">
+        <v>547</v>
+      </c>
       <c r="C43" s="3" t="s">
         <v>115</v>
       </c>
@@ -3821,10 +4942,13 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.8">
       <c r="A44" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="B44" t="s">
+        <v>548</v>
+      </c>
       <c r="C44" s="3" t="s">
         <v>118</v>
       </c>
@@ -3832,10 +4956,13 @@
         <v>119</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.8">
       <c r="A45" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="B45" t="s">
+        <v>549</v>
+      </c>
       <c r="C45" s="3" t="s">
         <v>121</v>
       </c>
@@ -3843,10 +4970,13 @@
         <v>122</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="A46" s="1" t="s">
         <v>123</v>
       </c>
+      <c r="B46" t="s">
+        <v>550</v>
+      </c>
       <c r="C46" s="3" t="s">
         <v>124</v>
       </c>
@@ -3854,10 +4984,13 @@
         <v>125</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="A47" s="1" t="s">
         <v>126</v>
       </c>
+      <c r="B47" t="s">
+        <v>551</v>
+      </c>
       <c r="C47" s="3" t="s">
         <v>127</v>
       </c>
@@ -3865,10 +4998,13 @@
         <v>128</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="A48" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="B48" t="s">
+        <v>552</v>
+      </c>
       <c r="C48" s="3" t="s">
         <v>130</v>
       </c>
@@ -3876,10 +5012,13 @@
         <v>131</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="A49" s="1" t="s">
         <v>132</v>
       </c>
+      <c r="B49" t="s">
+        <v>553</v>
+      </c>
       <c r="C49" s="3" t="s">
         <v>133</v>
       </c>
@@ -3887,10 +5026,13 @@
         <v>134</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="A50" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="B50" t="s">
+        <v>554</v>
+      </c>
       <c r="C50" s="3" t="s">
         <v>136</v>
       </c>
@@ -3898,10 +5040,13 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="22.35">
       <c r="A51" s="1" t="s">
         <v>138</v>
       </c>
+      <c r="B51" t="s">
+        <v>555</v>
+      </c>
       <c r="C51" s="3" t="s">
         <v>139</v>
       </c>
@@ -3909,10 +5054,13 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="12.8">
       <c r="A52" s="1" t="s">
         <v>141</v>
       </c>
+      <c r="B52" t="s">
+        <v>556</v>
+      </c>
       <c r="C52" s="3" t="s">
         <v>142</v>
       </c>
@@ -3920,10 +5068,13 @@
         <v>143</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" ht="12.8">
       <c r="A53" s="1" t="s">
         <v>144</v>
       </c>
+      <c r="B53" t="s">
+        <v>557</v>
+      </c>
       <c r="C53" s="3" t="s">
         <v>145</v>
       </c>
@@ -3931,10 +5082,13 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.8">
       <c r="A54" s="1" t="s">
         <v>147</v>
       </c>
+      <c r="B54" t="s">
+        <v>558</v>
+      </c>
       <c r="C54" s="3" t="s">
         <v>148</v>
       </c>
@@ -3942,10 +5096,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" ht="20.1" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>150</v>
       </c>
+      <c r="B55" t="s">
+        <v>559</v>
+      </c>
       <c r="C55" s="3" t="s">
         <v>151</v>
       </c>
@@ -3953,10 +5110,13 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" ht="20.1" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="B56" t="s">
+        <v>560</v>
+      </c>
       <c r="C56" s="3" t="s">
         <v>154</v>
       </c>
@@ -3964,10 +5124,13 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" ht="22.35">
       <c r="A57" s="1" t="s">
         <v>156</v>
       </c>
+      <c r="B57" t="s">
+        <v>561</v>
+      </c>
       <c r="C57" s="3" t="s">
         <v>157</v>
       </c>
@@ -3975,10 +5138,13 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="12.8">
       <c r="A58" s="1" t="s">
         <v>159</v>
       </c>
+      <c r="B58" t="s">
+        <v>562</v>
+      </c>
       <c r="C58" s="3" t="s">
         <v>160</v>
       </c>
@@ -3986,10 +5152,13 @@
         <v>161</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="12.8">
       <c r="A59" s="1" t="s">
         <v>162</v>
       </c>
+      <c r="B59" t="s">
+        <v>563</v>
+      </c>
       <c r="C59" s="3" t="s">
         <v>163</v>
       </c>
@@ -3997,10 +5166,13 @@
         <v>164</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="12.8">
       <c r="A60" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="B60" t="s">
+        <v>564</v>
+      </c>
       <c r="C60" s="3" t="s">
         <v>166</v>
       </c>
@@ -4008,10 +5180,13 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" ht="12.8">
       <c r="A61" s="1" t="s">
         <v>168</v>
       </c>
+      <c r="B61" t="s">
+        <v>565</v>
+      </c>
       <c r="C61" s="3" t="s">
         <v>169</v>
       </c>
@@ -4019,10 +5194,13 @@
         <v>170</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" ht="12.8">
       <c r="A62" s="1" t="s">
         <v>171</v>
       </c>
+      <c r="B62" t="s">
+        <v>566</v>
+      </c>
       <c r="C62" s="3" t="s">
         <v>172</v>
       </c>
@@ -4030,10 +5208,13 @@
         <v>173</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" ht="12.8">
       <c r="A63" s="1" t="s">
         <v>174</v>
       </c>
+      <c r="B63" t="s">
+        <v>567</v>
+      </c>
       <c r="C63" s="3" t="s">
         <v>175</v>
       </c>
@@ -4041,10 +5222,13 @@
         <v>176</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" ht="12.8">
       <c r="A64" s="1" t="s">
         <v>177</v>
       </c>
+      <c r="B64" t="s">
+        <v>568</v>
+      </c>
       <c r="C64" s="3" t="s">
         <v>178</v>
       </c>
@@ -4052,10 +5236,13 @@
         <v>179</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" ht="12.8">
       <c r="A65" s="1" t="s">
         <v>180</v>
       </c>
+      <c r="B65" t="s">
+        <v>569</v>
+      </c>
       <c r="C65" s="3" t="s">
         <v>181</v>
       </c>
@@ -4063,10 +5250,13 @@
         <v>182</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" ht="12.8">
       <c r="A66" s="1" t="s">
         <v>183</v>
       </c>
+      <c r="B66" t="s">
+        <v>570</v>
+      </c>
       <c r="C66" s="3" t="s">
         <v>184</v>
       </c>
@@ -4074,10 +5264,13 @@
         <v>185</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" ht="12.8">
       <c r="A67" s="1" t="s">
         <v>186</v>
       </c>
+      <c r="B67" t="s">
+        <v>571</v>
+      </c>
       <c r="C67" s="3" t="s">
         <v>187</v>
       </c>
@@ -4085,10 +5278,13 @@
         <v>188</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" ht="12.8">
       <c r="A68" s="1" t="s">
         <v>189</v>
       </c>
+      <c r="B68" t="s">
+        <v>572</v>
+      </c>
       <c r="C68" s="3" t="s">
         <v>190</v>
       </c>
@@ -4096,10 +5292,13 @@
         <v>191</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" ht="12.8">
       <c r="A69" s="1" t="s">
         <v>192</v>
       </c>
+      <c r="B69" t="s">
+        <v>573</v>
+      </c>
       <c r="C69" s="3" t="s">
         <v>193</v>
       </c>
@@ -4107,10 +5306,13 @@
         <v>194</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.8">
       <c r="A70" s="3" t="s">
         <v>195</v>
       </c>
+      <c r="B70" t="s">
+        <v>574</v>
+      </c>
       <c r="C70" s="3" t="s">
         <v>196</v>
       </c>
@@ -4118,10 +5320,13 @@
         <v>197</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="32.8">
       <c r="A71" s="1" t="s">
         <v>198</v>
       </c>
+      <c r="B71" t="s">
+        <v>575</v>
+      </c>
       <c r="C71" s="3" t="s">
         <v>199</v>
       </c>
@@ -4129,10 +5334,13 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" ht="32.8">
       <c r="A72" s="1" t="s">
         <v>201</v>
       </c>
+      <c r="B72" t="s">
+        <v>576</v>
+      </c>
       <c r="C72" s="3" t="s">
         <v>202</v>
       </c>
@@ -4140,10 +5348,13 @@
         <v>203</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="12.8">
       <c r="A73" s="1" t="s">
         <v>204</v>
       </c>
+      <c r="B73" t="s">
+        <v>577</v>
+      </c>
       <c r="C73" s="1" t="s">
         <v>205</v>
       </c>
@@ -4151,10 +5362,13 @@
         <v>206</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="12.8">
       <c r="A74" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="B74" t="s">
+        <v>578</v>
+      </c>
       <c r="C74" s="1" t="s">
         <v>208</v>
       </c>
@@ -4162,10 +5376,13 @@
         <v>209</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" ht="12.8">
       <c r="A75" s="1" t="s">
         <v>210</v>
       </c>
+      <c r="B75" t="s">
+        <v>579</v>
+      </c>
       <c r="C75" s="3" t="s">
         <v>211</v>
       </c>
@@ -4173,10 +5390,13 @@
         <v>212</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" ht="12.8">
       <c r="A76" s="1" t="s">
         <v>213</v>
       </c>
+      <c r="B76" t="s">
+        <v>580</v>
+      </c>
       <c r="C76" s="3" t="s">
         <v>214</v>
       </c>
@@ -4184,10 +5404,13 @@
         <v>215</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" ht="12.8">
       <c r="A77" s="1" t="s">
         <v>216</v>
       </c>
+      <c r="B77" t="s">
+        <v>581</v>
+      </c>
       <c r="C77" s="1" t="s">
         <v>217</v>
       </c>
@@ -4195,10 +5418,13 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" ht="12.8">
       <c r="A78" s="1" t="s">
         <v>219</v>
       </c>
+      <c r="B78" t="s">
+        <v>582</v>
+      </c>
       <c r="C78" s="1" t="s">
         <v>220</v>
       </c>
@@ -4206,10 +5432,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="22.35">
       <c r="A79" s="1" t="s">
         <v>222</v>
       </c>
+      <c r="B79" t="s">
+        <v>583</v>
+      </c>
       <c r="C79" s="3" t="s">
         <v>223</v>
       </c>
@@ -4217,10 +5446,13 @@
         <v>224</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" ht="12.8">
       <c r="A80" s="1" t="s">
         <v>225</v>
       </c>
+      <c r="B80" t="s">
+        <v>584</v>
+      </c>
       <c r="C80" s="3" t="s">
         <v>226</v>
       </c>
@@ -4228,10 +5460,13 @@
         <v>227</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" ht="12.8">
       <c r="A81" s="1" t="s">
         <v>228</v>
       </c>
+      <c r="B81" t="s">
+        <v>585</v>
+      </c>
       <c r="C81" s="1" t="s">
         <v>229</v>
       </c>
@@ -4239,10 +5474,13 @@
         <v>230</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" ht="12.8">
       <c r="A82" s="1" t="s">
         <v>231</v>
       </c>
+      <c r="B82" t="s">
+        <v>586</v>
+      </c>
       <c r="C82" s="1" t="s">
         <v>232</v>
       </c>
@@ -4250,10 +5488,13 @@
         <v>233</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" ht="12.8">
       <c r="A83" s="1" t="s">
         <v>234</v>
       </c>
+      <c r="B83" t="s">
+        <v>587</v>
+      </c>
       <c r="C83" s="1" t="s">
         <v>235</v>
       </c>
@@ -4261,10 +5502,13 @@
         <v>236</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" ht="12.8">
       <c r="A84" s="1" t="s">
         <v>237</v>
       </c>
+      <c r="B84" t="s">
+        <v>588</v>
+      </c>
       <c r="C84" s="1" t="s">
         <v>238</v>
       </c>
@@ -4272,10 +5516,13 @@
         <v>239</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" ht="12.8">
       <c r="A85" s="1" t="s">
         <v>240</v>
       </c>
+      <c r="B85" t="s">
+        <v>589</v>
+      </c>
       <c r="C85" s="1" t="s">
         <v>241</v>
       </c>
@@ -4283,10 +5530,13 @@
         <v>242</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="12.8">
       <c r="A86" s="1" t="s">
         <v>243</v>
       </c>
+      <c r="B86" t="s">
+        <v>590</v>
+      </c>
       <c r="C86" s="1" t="s">
         <v>244</v>
       </c>
@@ -4294,10 +5544,13 @@
         <v>245</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="12.8">
       <c r="A87" s="1" t="s">
         <v>246</v>
       </c>
+      <c r="B87" t="s">
+        <v>591</v>
+      </c>
       <c r="C87" s="1" t="s">
         <v>247</v>
       </c>
@@ -4305,10 +5558,13 @@
         <v>248</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" ht="12.8">
       <c r="A88" s="1" t="s">
         <v>249</v>
       </c>
+      <c r="B88" t="s">
+        <v>592</v>
+      </c>
       <c r="C88" s="1" t="s">
         <v>250</v>
       </c>
@@ -4316,66 +5572,11 @@
         <v>251</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -4384,20 +5585,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="13.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="117.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="122.68"/>
+    <col min="1" max="1" width="13.63" style="6" customWidth="1"/>
+    <col min="2" max="2" width="10.71" style="6" customWidth="1"/>
+    <col min="3" max="3" width="117.64" style="6" customWidth="1"/>
+    <col min="4" max="4" width="122.68" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -4411,242 +5612,301 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="12.8">
       <c r="C2" s="8"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="12.8">
       <c r="C3" s="8"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="12.8">
       <c r="C4" s="8"/>
     </row>
-    <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="74.6">
       <c r="A5" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" t="s">
+        <v>593</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" ht="43.25">
+      <c r="A6" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B6" t="s">
+        <v>594</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" ht="43.25">
+      <c r="A7" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" t="s">
+        <v>595</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" ht="43.25">
+      <c r="A8" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" t="s">
+        <v>596</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" ht="43.25">
+      <c r="A9" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9" t="s">
+        <v>597</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" ht="74.6">
+      <c r="A10" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="B10" t="s">
+        <v>598</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    <row r="11" ht="43.25">
+      <c r="A11" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="B11" t="s">
+        <v>599</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    <row r="12" ht="43.25">
+      <c r="A12" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="B12" t="s">
+        <v>600</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    <row r="13" ht="95.5">
+      <c r="A13" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="B13" t="s">
+        <v>601</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="14" ht="32.8">
+      <c r="A14" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="B14" t="s">
+        <v>602</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="15" ht="32.8">
+      <c r="A15" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="B15" t="s">
+        <v>603</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="16" ht="12.8">
+      <c r="A16" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="B16" t="s">
+        <v>604</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    <row r="17" ht="22.35">
+      <c r="A17" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="B17" t="s">
+        <v>605</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    <row r="18" ht="22.35">
+      <c r="A18" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="B18" t="s">
+        <v>606</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="19" ht="200.7">
+      <c r="A19" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="B19" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" ht="168.65">
+      <c r="A20" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="B20" t="s">
+        <v>608</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+    <row r="21" ht="241.75">
+      <c r="A21" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="B21" t="s">
+        <v>609</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D21" s="8" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    <row r="22" ht="32.8">
+      <c r="A22" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="B22" t="s">
+        <v>610</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    <row r="23" ht="22.35">
+      <c r="A23" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="B23" t="s">
+        <v>611</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="200.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+    <row r="24" ht="231.3">
+      <c r="A24" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8" t="s">
+      <c r="B24" t="s">
+        <v>612</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>326</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -4654,20 +5914,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="109.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="123.06"/>
+    <col min="1" max="1" width="15.7" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.61" style="1" customWidth="1"/>
+    <col min="3" max="3" width="109.15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="123.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4681,158 +5941,193 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="64.15">
       <c r="A5" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B5" t="s">
+        <v>613</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6" ht="53.7">
+      <c r="A6" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B6" t="s">
+        <v>614</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" ht="22.35">
+      <c r="A7" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B7" t="s">
+        <v>615</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" ht="64.15">
+      <c r="A8" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B8" t="s">
+        <v>616</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="9" ht="64.15">
+      <c r="A9" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B9" t="s">
+        <v>617</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="10" ht="95.5">
+      <c r="A10" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B10" t="s">
+        <v>618</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="11" ht="64.15">
+      <c r="A11" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B11" t="s">
+        <v>619</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="12" ht="53.7">
+      <c r="A12" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B12" t="s">
+        <v>620</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+    <row r="13" ht="74.6">
+      <c r="A13" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B13" t="s">
+        <v>621</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="14" ht="116.4">
+      <c r="A14" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B14" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="15" ht="147.75">
+      <c r="A15" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="B15" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+    <row r="16" ht="116.4">
+      <c r="A16" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="B16" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+    <row r="17" ht="168.65">
+      <c r="A17" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -4840,20 +6135,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="139.81"/>
+    <col min="1" max="1" width="14.58" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.56" style="1" customWidth="1"/>
+    <col min="3" max="3" width="110.96" style="1" customWidth="1"/>
+    <col min="4" max="4" width="139.81" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4867,521 +6162,650 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="12.8">
       <c r="C2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="12.8">
       <c r="C3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="12.8">
       <c r="C4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="53.7">
       <c r="A5" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B5" t="s">
+        <v>626</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" ht="126.85">
+      <c r="A6" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B6" t="s">
+        <v>627</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" ht="12.8">
+      <c r="A7" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B7" t="s">
+        <v>628</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" ht="126.85">
+      <c r="A8" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="9" ht="105.95">
+      <c r="A9" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B9" t="s">
+        <v>630</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="10" ht="105.95">
+      <c r="A10" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B10" t="s">
+        <v>631</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="11" ht="116.4">
+      <c r="A11" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B11" t="s">
+        <v>632</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="12" ht="43.25">
+      <c r="A12" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B12" t="s">
+        <v>633</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+    <row r="13" ht="32.8">
+      <c r="A13" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B13" t="s">
+        <v>634</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="14" ht="64.15">
+      <c r="A14" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="15" ht="22.35">
+      <c r="A15" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="B15" t="s">
+        <v>636</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+    <row r="16" ht="43.25">
+      <c r="A16" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="B16" t="s">
+        <v>637</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+    <row r="17" ht="32.8">
+      <c r="A17" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="B17" t="s">
+        <v>638</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+    <row r="18" ht="43.25">
+      <c r="A18" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="B18" t="s">
+        <v>639</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="19" ht="53.7">
+      <c r="A19" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="B19" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="20" ht="12.8">
+      <c r="A20" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="B20" t="s">
+        <v>641</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="21" ht="43.25">
+      <c r="A21" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="B21" t="s">
+        <v>642</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="22" ht="32.8">
+      <c r="A22" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="B22" t="s">
+        <v>643</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="23" ht="32.8">
+      <c r="A23" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="B23" t="s">
+        <v>644</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="24" ht="32.8">
+      <c r="A24" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3" t="s">
+      <c r="B24" t="s">
+        <v>645</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="25" ht="44.75">
+      <c r="A25" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="B25" t="s">
+        <v>646</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="26" ht="32.8">
+      <c r="A26" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="B26" t="s">
+        <v>647</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="27" ht="56.7">
+      <c r="A27" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="B27" t="s">
+        <v>648</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="28" ht="79.1">
+      <c r="A28" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="B28" t="s">
+        <v>649</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D28" s="10" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+    <row r="29" ht="44.75">
+      <c r="A29" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="B29" t="s">
+        <v>650</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="30" ht="13.8">
+      <c r="A30" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="B30" t="s">
+        <v>651</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D30" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    <row r="31" ht="179.1">
+      <c r="A31" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="B31" t="s">
+        <v>652</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+    <row r="32" ht="12.8">
+      <c r="A32" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="B32" t="s">
+        <v>653</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="13.8">
       <c r="A33" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B33" t="s">
+        <v>654</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="34" ht="91">
+      <c r="A34" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="B34" t="s">
+        <v>655</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="35" ht="12.8">
+      <c r="A35" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B35" t="s">
+        <v>656</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="36" ht="105.95">
+      <c r="A36" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" ht="126.85">
+      <c r="A37" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="38" ht="126.85">
+      <c r="A38" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="B38" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D38" s="3" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
+    <row r="39" ht="22.35">
+      <c r="A39" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="B39" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+    <row r="40" ht="74.6">
+      <c r="A40" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D40" s="3" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+    <row r="41" ht="105.95">
+      <c r="A41" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="3" t="s">
+      <c r="B41" t="s">
+        <v>662</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+    <row r="42" ht="105.95">
+      <c r="A42" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="3" t="s">
+      <c r="B42" t="s">
+        <v>663</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+    <row r="43" ht="105.95">
+      <c r="A43" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="3" t="s">
+      <c r="B43" t="s">
+        <v>664</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
+    <row r="44" ht="105.95">
+      <c r="A44" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5" t="s">
+      <c r="B44" t="s">
+        <v>665</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+    <row r="45" ht="95.5">
+      <c r="A45" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="3" t="s">
+      <c r="B45" t="s">
+        <v>666</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+    <row r="46" ht="116.4">
+      <c r="A46" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="B46" t="s">
+        <v>667</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+    <row r="47" ht="105.95">
+      <c r="A47" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="B47" t="s">
+        <v>668</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
+    <row r="48" ht="105.95">
+      <c r="A48" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="B48" t="s">
+        <v>669</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
+    <row r="49" ht="95.5">
+      <c r="A49" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="B49" t="s">
+        <v>670</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -5389,20 +6813,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="100.58"/>
+    <col min="1" max="1" width="14.58" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.56" style="1" customWidth="1"/>
+    <col min="3" max="3" width="110.96" style="1" customWidth="1"/>
+    <col min="4" max="4" width="100.58" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5416,108 +6840,132 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="12.8">
       <c r="C2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="12.8">
       <c r="C3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="12.8">
       <c r="C4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="32.8">
       <c r="A5" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>671</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="6" ht="168.65">
+      <c r="A6" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B6" t="s">
+        <v>672</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="7" ht="220.85">
+      <c r="A7" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B7" t="s">
+        <v>673</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="8" ht="231.3">
+      <c r="A8" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B8" t="s">
+        <v>674</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="9" ht="210.4">
+      <c r="A9" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B9" t="s">
+        <v>675</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="10" ht="314.9">
+      <c r="A10" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B10" t="s">
+        <v>676</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="11" ht="112.65">
+      <c r="A11" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B11" t="s">
+        <v>677</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="12" ht="199.95">
+      <c r="A12" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B12" t="s">
+        <v>678</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>523</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
